--- a/reports/calculs_obligataires.xlsx
+++ b/reports/calculs_obligataires.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -457,12 +457,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Feuille Chocs : les six scénarios IRRBB (CAD : 200/250/200 pb, BCBS 2024) revalorisent l'obligation.</t>
+          <t>L'échéance est arrondie au pas de coupon le plus proche (0,5 an par défaut) et plafonne à 30 ans.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>Feuille Chocs : les six scénarios IRRBB (CAD : 200/275/175 pb, BCBS d578 2024) revalorisent l'obligation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Les formules sont vivantes : aucun chiffre collé, tout part de la feuille Courbe.</t>
         </is>
@@ -1561,11 +1568,11 @@
         <v/>
       </c>
       <c r="B8">
-        <f>IF(A8&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A8=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A8*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A8*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C8">
-        <f>VLOOKUP(A8,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A8,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D8">
@@ -1587,11 +1594,11 @@
         <v/>
       </c>
       <c r="B9">
-        <f>IF(A9&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A9=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A9*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A9*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C9">
-        <f>VLOOKUP(A9,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A9,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D9">
@@ -1613,11 +1620,11 @@
         <v/>
       </c>
       <c r="B10">
-        <f>IF(A10&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A10=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A10*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A10*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C10">
-        <f>VLOOKUP(A10,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A10,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D10">
@@ -1639,11 +1646,11 @@
         <v/>
       </c>
       <c r="B11">
-        <f>IF(A11&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A11=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A11*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A11*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C11">
-        <f>VLOOKUP(A11,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A11,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D11">
@@ -1665,11 +1672,11 @@
         <v/>
       </c>
       <c r="B12">
-        <f>IF(A12&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A12=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A12*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A12*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C12">
-        <f>VLOOKUP(A12,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A12,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D12">
@@ -1691,11 +1698,11 @@
         <v/>
       </c>
       <c r="B13">
-        <f>IF(A13&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A13=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A13*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A13*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C13">
-        <f>VLOOKUP(A13,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A13,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D13">
@@ -1717,11 +1724,11 @@
         <v/>
       </c>
       <c r="B14">
-        <f>IF(A14&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A14=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A14*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A14*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C14">
-        <f>VLOOKUP(A14,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A14,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D14">
@@ -1743,11 +1750,11 @@
         <v/>
       </c>
       <c r="B15">
-        <f>IF(A15&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A15=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A15*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A15*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C15">
-        <f>VLOOKUP(A15,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A15,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D15">
@@ -1769,11 +1776,11 @@
         <v/>
       </c>
       <c r="B16">
-        <f>IF(A16&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A16=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A16*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A16*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C16">
-        <f>VLOOKUP(A16,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A16,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D16">
@@ -1795,11 +1802,11 @@
         <v/>
       </c>
       <c r="B17">
-        <f>IF(A17&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A17=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A17*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A17*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C17">
-        <f>VLOOKUP(A17,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A17,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D17">
@@ -1821,11 +1828,11 @@
         <v/>
       </c>
       <c r="B18">
-        <f>IF(A18&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A18=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A18*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A18*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C18">
-        <f>VLOOKUP(A18,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A18,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D18">
@@ -1847,11 +1854,11 @@
         <v/>
       </c>
       <c r="B19">
-        <f>IF(A19&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A19=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A19*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A19*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C19">
-        <f>VLOOKUP(A19,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A19,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D19">
@@ -1873,11 +1880,11 @@
         <v/>
       </c>
       <c r="B20">
-        <f>IF(A20&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A20=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A20*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A20*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C20">
-        <f>VLOOKUP(A20,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A20,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D20">
@@ -1899,11 +1906,11 @@
         <v/>
       </c>
       <c r="B21">
-        <f>IF(A21&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A21=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A21*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A21*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C21">
-        <f>VLOOKUP(A21,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A21,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D21">
@@ -1925,11 +1932,11 @@
         <v/>
       </c>
       <c r="B22">
-        <f>IF(A22&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A22=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A22*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A22*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C22">
-        <f>VLOOKUP(A22,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A22,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D22">
@@ -1951,11 +1958,11 @@
         <v/>
       </c>
       <c r="B23">
-        <f>IF(A23&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A23=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A23*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A23*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C23">
-        <f>VLOOKUP(A23,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A23,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D23">
@@ -1977,11 +1984,11 @@
         <v/>
       </c>
       <c r="B24">
-        <f>IF(A24&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A24=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A24*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A24*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C24">
-        <f>VLOOKUP(A24,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A24,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D24">
@@ -2003,11 +2010,11 @@
         <v/>
       </c>
       <c r="B25">
-        <f>IF(A25&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A25=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A25*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A25*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C25">
-        <f>VLOOKUP(A25,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A25,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D25">
@@ -2029,11 +2036,11 @@
         <v/>
       </c>
       <c r="B26">
-        <f>IF(A26&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A26=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A26*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A26*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C26">
-        <f>VLOOKUP(A26,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A26,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D26">
@@ -2055,11 +2062,11 @@
         <v/>
       </c>
       <c r="B27">
-        <f>IF(A27&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A27=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A27*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A27*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C27">
-        <f>VLOOKUP(A27,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A27,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D27">
@@ -2081,11 +2088,11 @@
         <v/>
       </c>
       <c r="B28">
-        <f>IF(A28&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A28=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A28*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A28*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C28">
-        <f>VLOOKUP(A28,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A28,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D28">
@@ -2107,11 +2114,11 @@
         <v/>
       </c>
       <c r="B29">
-        <f>IF(A29&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A29=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A29*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A29*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C29">
-        <f>VLOOKUP(A29,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A29,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D29">
@@ -2133,11 +2140,11 @@
         <v/>
       </c>
       <c r="B30">
-        <f>IF(A30&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A30=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A30*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A30*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C30">
-        <f>VLOOKUP(A30,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A30,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D30">
@@ -2159,11 +2166,11 @@
         <v/>
       </c>
       <c r="B31">
-        <f>IF(A31&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A31=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A31*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A31*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C31">
-        <f>VLOOKUP(A31,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A31,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D31">
@@ -2185,11 +2192,11 @@
         <v/>
       </c>
       <c r="B32">
-        <f>IF(A32&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A32=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A32*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A32*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C32">
-        <f>VLOOKUP(A32,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A32,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D32">
@@ -2211,11 +2218,11 @@
         <v/>
       </c>
       <c r="B33">
-        <f>IF(A33&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A33=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A33*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A33*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C33">
-        <f>VLOOKUP(A33,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A33,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D33">
@@ -2237,11 +2244,11 @@
         <v/>
       </c>
       <c r="B34">
-        <f>IF(A34&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A34=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A34*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A34*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C34">
-        <f>VLOOKUP(A34,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A34,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D34">
@@ -2263,11 +2270,11 @@
         <v/>
       </c>
       <c r="B35">
-        <f>IF(A35&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A35=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A35*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A35*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C35">
-        <f>VLOOKUP(A35,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A35,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D35">
@@ -2289,11 +2296,11 @@
         <v/>
       </c>
       <c r="B36">
-        <f>IF(A36&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A36=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A36*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A36*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C36">
-        <f>VLOOKUP(A36,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A36,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D36">
@@ -2315,11 +2322,11 @@
         <v/>
       </c>
       <c r="B37">
-        <f>IF(A37&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A37=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A37*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A37*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C37">
-        <f>VLOOKUP(A37,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A37,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D37">
@@ -2341,11 +2348,11 @@
         <v/>
       </c>
       <c r="B38">
-        <f>IF(A38&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A38=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A38*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A38*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C38">
-        <f>VLOOKUP(A38,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A38,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D38">
@@ -2367,11 +2374,11 @@
         <v/>
       </c>
       <c r="B39">
-        <f>IF(A39&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A39=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A39*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A39*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C39">
-        <f>VLOOKUP(A39,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A39,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D39">
@@ -2393,11 +2400,11 @@
         <v/>
       </c>
       <c r="B40">
-        <f>IF(A40&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A40=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A40*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A40*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C40">
-        <f>VLOOKUP(A40,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A40,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D40">
@@ -2419,11 +2426,11 @@
         <v/>
       </c>
       <c r="B41">
-        <f>IF(A41&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A41=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A41*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A41*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C41">
-        <f>VLOOKUP(A41,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A41,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D41">
@@ -2445,11 +2452,11 @@
         <v/>
       </c>
       <c r="B42">
-        <f>IF(A42&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A42=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A42*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A42*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C42">
-        <f>VLOOKUP(A42,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A42,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D42">
@@ -2471,11 +2478,11 @@
         <v/>
       </c>
       <c r="B43">
-        <f>IF(A43&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A43=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A43*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A43*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C43">
-        <f>VLOOKUP(A43,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A43,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D43">
@@ -2497,11 +2504,11 @@
         <v/>
       </c>
       <c r="B44">
-        <f>IF(A44&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A44=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A44*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A44*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C44">
-        <f>VLOOKUP(A44,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A44,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D44">
@@ -2523,11 +2530,11 @@
         <v/>
       </c>
       <c r="B45">
-        <f>IF(A45&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A45=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A45*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A45*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C45">
-        <f>VLOOKUP(A45,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A45,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D45">
@@ -2549,11 +2556,11 @@
         <v/>
       </c>
       <c r="B46">
-        <f>IF(A46&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A46=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A46*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A46*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C46">
-        <f>VLOOKUP(A46,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A46,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D46">
@@ -2575,11 +2582,11 @@
         <v/>
       </c>
       <c r="B47">
-        <f>IF(A47&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A47=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A47*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A47*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C47">
-        <f>VLOOKUP(A47,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A47,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D47">
@@ -2601,11 +2608,11 @@
         <v/>
       </c>
       <c r="B48">
-        <f>IF(A48&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A48=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A48*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A48*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C48">
-        <f>VLOOKUP(A48,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A48,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D48">
@@ -2627,11 +2634,11 @@
         <v/>
       </c>
       <c r="B49">
-        <f>IF(A49&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A49=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A49*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A49*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C49">
-        <f>VLOOKUP(A49,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A49,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D49">
@@ -2653,11 +2660,11 @@
         <v/>
       </c>
       <c r="B50">
-        <f>IF(A50&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A50=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A50*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A50*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C50">
-        <f>VLOOKUP(A50,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A50,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D50">
@@ -2679,11 +2686,11 @@
         <v/>
       </c>
       <c r="B51">
-        <f>IF(A51&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A51=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A51*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A51*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C51">
-        <f>VLOOKUP(A51,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A51,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D51">
@@ -2705,11 +2712,11 @@
         <v/>
       </c>
       <c r="B52">
-        <f>IF(A52&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A52=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A52*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A52*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C52">
-        <f>VLOOKUP(A52,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A52,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D52">
@@ -2731,11 +2738,11 @@
         <v/>
       </c>
       <c r="B53">
-        <f>IF(A53&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A53=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A53*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A53*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C53">
-        <f>VLOOKUP(A53,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A53,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D53">
@@ -2757,11 +2764,11 @@
         <v/>
       </c>
       <c r="B54">
-        <f>IF(A54&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A54=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A54*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A54*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C54">
-        <f>VLOOKUP(A54,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A54,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D54">
@@ -2783,11 +2790,11 @@
         <v/>
       </c>
       <c r="B55">
-        <f>IF(A55&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A55=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A55*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A55*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C55">
-        <f>VLOOKUP(A55,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A55,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D55">
@@ -2809,11 +2816,11 @@
         <v/>
       </c>
       <c r="B56">
-        <f>IF(A56&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A56=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A56*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A56*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C56">
-        <f>VLOOKUP(A56,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A56,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D56">
@@ -2835,11 +2842,11 @@
         <v/>
       </c>
       <c r="B57">
-        <f>IF(A57&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A57=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A57*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A57*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C57">
-        <f>VLOOKUP(A57,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A57,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D57">
@@ -2861,11 +2868,11 @@
         <v/>
       </c>
       <c r="B58">
-        <f>IF(A58&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A58=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A58*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A58*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C58">
-        <f>VLOOKUP(A58,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A58,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D58">
@@ -2887,11 +2894,11 @@
         <v/>
       </c>
       <c r="B59">
-        <f>IF(A59&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A59=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A59*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A59*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C59">
-        <f>VLOOKUP(A59,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A59,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D59">
@@ -2913,11 +2920,11 @@
         <v/>
       </c>
       <c r="B60">
-        <f>IF(A60&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A60=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A60*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A60*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C60">
-        <f>VLOOKUP(A60,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A60,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D60">
@@ -2939,11 +2946,11 @@
         <v/>
       </c>
       <c r="B61">
-        <f>IF(A61&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A61=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A61*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A61*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C61">
-        <f>VLOOKUP(A61,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A61,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D61">
@@ -2965,11 +2972,11 @@
         <v/>
       </c>
       <c r="B62">
-        <f>IF(A62&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A62=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A62*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A62*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C62">
-        <f>VLOOKUP(A62,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A62,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D62">
@@ -2991,11 +2998,11 @@
         <v/>
       </c>
       <c r="B63">
-        <f>IF(A63&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A63=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A63*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A63*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C63">
-        <f>VLOOKUP(A63,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A63,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D63">
@@ -3017,11 +3024,11 @@
         <v/>
       </c>
       <c r="B64">
-        <f>IF(A64&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A64=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A64*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A64*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C64">
-        <f>VLOOKUP(A64,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A64,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D64">
@@ -3043,11 +3050,11 @@
         <v/>
       </c>
       <c r="B65">
-        <f>IF(A65&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A65=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A65*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A65*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C65">
-        <f>VLOOKUP(A65,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A65,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D65">
@@ -3069,11 +3076,11 @@
         <v/>
       </c>
       <c r="B66">
-        <f>IF(A66&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A66=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A66*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A66*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C66">
-        <f>VLOOKUP(A66,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A66,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D66">
@@ -3095,11 +3102,11 @@
         <v/>
       </c>
       <c r="B67">
-        <f>IF(A67&gt;$B$3,0,$B$4*$B$2/100/$B$5+IF(A67=$B$3,$B$4,0))</f>
+        <f>IF(ROUND(A67*$B$5,0)&gt;ROUND($B$3*$B$5,0),0,$B$4*$B$2/100/$B$5+IF(ROUND(A67*$B$5,0)=ROUND($B$3*$B$5,0),$B$4,0))</f>
         <v/>
       </c>
       <c r="C67">
-        <f>VLOOKUP(A67,Courbe!$A$2:$B$121,2,FALSE)</f>
+        <f>IFERROR(VLOOKUP(A67,Courbe!$A$2:$B$121,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="D67">
@@ -3213,19 +3220,19 @@
         <v/>
       </c>
       <c r="E2">
-        <f>$B2+-1.4175</f>
+        <f>$B2+-1.5838</f>
         <v/>
       </c>
       <c r="F2">
-        <f>$B2+1.8061</f>
+        <f>$B2+2.0031</f>
         <v/>
       </c>
       <c r="G2">
-        <f>$B2+2.3485</f>
+        <f>$B2+2.5834</f>
         <v/>
       </c>
       <c r="H2">
-        <f>$B2+-2.3485</f>
+        <f>$B2+-2.5834</f>
         <v/>
       </c>
     </row>
@@ -3246,19 +3253,19 @@
         <v/>
       </c>
       <c r="E3">
-        <f>$B3+-1.2226</f>
+        <f>$B3+-1.3924</f>
         <v/>
       </c>
       <c r="F3">
-        <f>$B3+1.624</f>
+        <f>$B3+1.8181</f>
         <v/>
       </c>
       <c r="G3">
-        <f>$B3+2.2062</f>
+        <f>$B3+2.4269</f>
         <v/>
       </c>
       <c r="H3">
-        <f>$B3+-2.2062</f>
+        <f>$B3+-2.4269</f>
         <v/>
       </c>
     </row>
@@ -3279,19 +3286,19 @@
         <v/>
       </c>
       <c r="E4">
-        <f>$B4+-1.0394</f>
+        <f>$B4+-1.2126</f>
         <v/>
       </c>
       <c r="F4">
-        <f>$B4+1.4529</f>
+        <f>$B4+1.6443</f>
         <v/>
       </c>
       <c r="G4">
-        <f>$B4+2.0726</f>
+        <f>$B4+2.2798</f>
         <v/>
       </c>
       <c r="H4">
-        <f>$B4+-2.0726</f>
+        <f>$B4+-2.2798</f>
         <v/>
       </c>
     </row>
@@ -3312,19 +3319,19 @@
         <v/>
       </c>
       <c r="E5">
-        <f>$B5+-0.8674</f>
+        <f>$B5+-1.0437</f>
         <v/>
       </c>
       <c r="F5">
-        <f>$B5+1.2922</f>
+        <f>$B5+1.4811</f>
         <v/>
       </c>
       <c r="G5">
-        <f>$B5+1.947</f>
+        <f>$B5+2.1417</f>
         <v/>
       </c>
       <c r="H5">
-        <f>$B5+-1.947</f>
+        <f>$B5+-2.1417</f>
         <v/>
       </c>
     </row>
@@ -3345,19 +3352,19 @@
         <v/>
       </c>
       <c r="E6">
-        <f>$B6+-0.7058</f>
+        <f>$B6+-0.8851</f>
         <v/>
       </c>
       <c r="F6">
-        <f>$B6+1.1412</f>
+        <f>$B6+1.3278</f>
         <v/>
       </c>
       <c r="G6">
-        <f>$B6+1.829</f>
+        <f>$B6+2.0119</f>
         <v/>
       </c>
       <c r="H6">
-        <f>$B6+-1.829</f>
+        <f>$B6+-2.0119</f>
         <v/>
       </c>
     </row>
@@ -3378,19 +3385,19 @@
         <v/>
       </c>
       <c r="E7">
-        <f>$B7+-0.554</f>
+        <f>$B7+-0.736</f>
         <v/>
       </c>
       <c r="F7">
-        <f>$B7+0.9993</f>
+        <f>$B7+1.1837</f>
         <v/>
       </c>
       <c r="G7">
-        <f>$B7+1.7182</f>
+        <f>$B7+1.89</f>
         <v/>
       </c>
       <c r="H7">
-        <f>$B7+-1.7182</f>
+        <f>$B7+-1.89</f>
         <v/>
       </c>
     </row>
@@ -3411,19 +3418,19 @@
         <v/>
       </c>
       <c r="E8">
-        <f>$B8+-0.4113</f>
+        <f>$B8+-0.596</f>
         <v/>
       </c>
       <c r="F8">
-        <f>$B8+0.8661</f>
+        <f>$B8+1.0484</f>
         <v/>
       </c>
       <c r="G8">
-        <f>$B8+1.6141</f>
+        <f>$B8+1.7755</f>
         <v/>
       </c>
       <c r="H8">
-        <f>$B8+-1.6141</f>
+        <f>$B8+-1.7755</f>
         <v/>
       </c>
     </row>
@@ -3444,19 +3451,19 @@
         <v/>
       </c>
       <c r="E9">
-        <f>$B9+-0.2774</f>
+        <f>$B9+-0.4645</f>
         <v/>
       </c>
       <c r="F9">
-        <f>$B9+0.7409</f>
+        <f>$B9+0.9212</f>
         <v/>
       </c>
       <c r="G9">
-        <f>$B9+1.5163</f>
+        <f>$B9+1.668</f>
         <v/>
       </c>
       <c r="H9">
-        <f>$B9+-1.5163</f>
+        <f>$B9+-1.668</f>
         <v/>
       </c>
     </row>
@@ -3477,19 +3484,19 @@
         <v/>
       </c>
       <c r="E10">
-        <f>$B10+-0.1515</f>
+        <f>$B10+-0.3409</f>
         <v/>
       </c>
       <c r="F10">
-        <f>$B10+0.6233</f>
+        <f>$B10+0.8018</f>
         <v/>
       </c>
       <c r="G10">
-        <f>$B10+1.4245</f>
+        <f>$B10+1.5669</f>
         <v/>
       </c>
       <c r="H10">
-        <f>$B10+-1.4245</f>
+        <f>$B10+-1.5669</f>
         <v/>
       </c>
     </row>
@@ -3510,19 +3517,19 @@
         <v/>
       </c>
       <c r="E11">
-        <f>$B11+-0.0333</f>
+        <f>$B11+-0.2248</f>
         <v/>
       </c>
       <c r="F11">
-        <f>$B11+0.5128</f>
+        <f>$B11+0.6896</f>
         <v/>
       </c>
       <c r="G11">
-        <f>$B11+1.3382</f>
+        <f>$B11+1.472</f>
         <v/>
       </c>
       <c r="H11">
-        <f>$B11+-1.3382</f>
+        <f>$B11+-1.472</f>
         <v/>
       </c>
     </row>
@@ -3543,19 +3550,19 @@
         <v/>
       </c>
       <c r="E12">
-        <f>$B12+0.0778</f>
+        <f>$B12+-0.1158</f>
         <v/>
       </c>
       <c r="F12">
-        <f>$B12+0.4091</f>
+        <f>$B12+0.5842</f>
         <v/>
       </c>
       <c r="G12">
-        <f>$B12+1.2571</f>
+        <f>$B12+1.3828</f>
         <v/>
       </c>
       <c r="H12">
-        <f>$B12+-1.2571</f>
+        <f>$B12+-1.3828</f>
         <v/>
       </c>
     </row>
@@ -3576,19 +3583,19 @@
         <v/>
       </c>
       <c r="E13">
-        <f>$B13+0.1821</f>
+        <f>$B13+-0.0133</f>
         <v/>
       </c>
       <c r="F13">
-        <f>$B13+0.3116</f>
+        <f>$B13+0.4852</f>
         <v/>
       </c>
       <c r="G13">
-        <f>$B13+1.1809</f>
+        <f>$B13+1.299</f>
         <v/>
       </c>
       <c r="H13">
-        <f>$B13+-1.1809</f>
+        <f>$B13+-1.299</f>
         <v/>
       </c>
     </row>
@@ -3609,19 +3616,19 @@
         <v/>
       </c>
       <c r="E14">
-        <f>$B14+0.2802</f>
+        <f>$B14+0.0829</f>
         <v/>
       </c>
       <c r="F14">
-        <f>$B14+0.22</f>
+        <f>$B14+0.3922</f>
         <v/>
       </c>
       <c r="G14">
-        <f>$B14+1.1094</f>
+        <f>$B14+1.2203</f>
         <v/>
       </c>
       <c r="H14">
-        <f>$B14+-1.1094</f>
+        <f>$B14+-1.2203</f>
         <v/>
       </c>
     </row>
@@ -3642,19 +3649,19 @@
         <v/>
       </c>
       <c r="E15">
-        <f>$B15+0.3722</f>
+        <f>$B15+0.1733</f>
         <v/>
       </c>
       <c r="F15">
-        <f>$B15+0.134</f>
+        <f>$B15+0.3048</f>
         <v/>
       </c>
       <c r="G15">
-        <f>$B15+1.0422</f>
+        <f>$B15+1.1464</f>
         <v/>
       </c>
       <c r="H15">
-        <f>$B15+-1.0422</f>
+        <f>$B15+-1.1464</f>
         <v/>
       </c>
     </row>
@@ -3675,19 +3682,19 @@
         <v/>
       </c>
       <c r="E16">
-        <f>$B16+0.4588</f>
+        <f>$B16+0.2582</f>
         <v/>
       </c>
       <c r="F16">
-        <f>$B16+0.0531</f>
+        <f>$B16+0.2227</f>
         <v/>
       </c>
       <c r="G16">
-        <f>$B16+0.979</f>
+        <f>$B16+1.0769</f>
         <v/>
       </c>
       <c r="H16">
-        <f>$B16+-0.979</f>
+        <f>$B16+-1.0769</f>
         <v/>
       </c>
     </row>
@@ -3708,19 +3715,19 @@
         <v/>
       </c>
       <c r="E17">
-        <f>$B17+0.54</f>
+        <f>$B17+0.338</f>
         <v/>
       </c>
       <c r="F17">
-        <f>$B17+-0.0228</f>
+        <f>$B17+0.1456</f>
         <v/>
       </c>
       <c r="G17">
-        <f>$B17+0.9197</f>
+        <f>$B17+1.0117</f>
         <v/>
       </c>
       <c r="H17">
-        <f>$B17+-0.9197</f>
+        <f>$B17+-1.0117</f>
         <v/>
       </c>
     </row>
@@ -3741,19 +3748,19 @@
         <v/>
       </c>
       <c r="E18">
-        <f>$B18+0.6164</f>
+        <f>$B18+0.413</f>
         <v/>
       </c>
       <c r="F18">
-        <f>$B18+-0.0941</f>
+        <f>$B18+0.0732</f>
         <v/>
       </c>
       <c r="G18">
-        <f>$B18+0.864</f>
+        <f>$B18+0.9504</f>
         <v/>
       </c>
       <c r="H18">
-        <f>$B18+-0.864</f>
+        <f>$B18+-0.9504</f>
         <v/>
       </c>
     </row>
@@ -3774,19 +3781,19 @@
         <v/>
       </c>
       <c r="E19">
-        <f>$B19+0.6881</f>
+        <f>$B19+0.4834</f>
         <v/>
       </c>
       <c r="F19">
-        <f>$B19+-0.1611</f>
+        <f>$B19+0.0051</f>
         <v/>
       </c>
       <c r="G19">
-        <f>$B19+0.8116</f>
+        <f>$B19+0.8928</f>
         <v/>
       </c>
       <c r="H19">
-        <f>$B19+-0.8116</f>
+        <f>$B19+-0.8928</f>
         <v/>
       </c>
     </row>
@@ -3807,19 +3814,19 @@
         <v/>
       </c>
       <c r="E20">
-        <f>$B20+0.7554</f>
+        <f>$B20+0.5495</f>
         <v/>
       </c>
       <c r="F20">
-        <f>$B20+-0.2241</f>
+        <f>$B20+-0.0588</f>
         <v/>
       </c>
       <c r="G20">
-        <f>$B20+0.7625</f>
+        <f>$B20+0.8387</f>
         <v/>
       </c>
       <c r="H20">
-        <f>$B20+-0.7625</f>
+        <f>$B20+-0.8387</f>
         <v/>
       </c>
     </row>
@@ -3840,19 +3847,19 @@
         <v/>
       </c>
       <c r="E21">
-        <f>$B21+0.8187</f>
+        <f>$B21+0.6116</f>
         <v/>
       </c>
       <c r="F21">
-        <f>$B21+-0.2832</f>
+        <f>$B21+-0.1189</f>
         <v/>
       </c>
       <c r="G21">
-        <f>$B21+0.7163</f>
+        <f>$B21+0.7879</f>
         <v/>
       </c>
       <c r="H21">
-        <f>$B21+-0.7163</f>
+        <f>$B21+-0.7879</f>
         <v/>
       </c>
     </row>
@@ -3873,19 +3880,19 @@
         <v/>
       </c>
       <c r="E22">
-        <f>$B22+0.8782</f>
+        <f>$B22+0.67</f>
         <v/>
       </c>
       <c r="F22">
-        <f>$B22+-0.3387</f>
+        <f>$B22+-0.1753</f>
         <v/>
       </c>
       <c r="G22">
-        <f>$B22+0.6729</f>
+        <f>$B22+0.7402</f>
         <v/>
       </c>
       <c r="H22">
-        <f>$B22+-0.6729</f>
+        <f>$B22+-0.7402</f>
         <v/>
       </c>
     </row>
@@ -3906,19 +3913,19 @@
         <v/>
       </c>
       <c r="E23">
-        <f>$B23+0.934</f>
+        <f>$B23+0.7248</f>
         <v/>
       </c>
       <c r="F23">
-        <f>$B23+-0.3909</f>
+        <f>$B23+-0.2283</f>
         <v/>
       </c>
       <c r="G23">
-        <f>$B23+0.6321</f>
+        <f>$B23+0.6953</f>
         <v/>
       </c>
       <c r="H23">
-        <f>$B23+-0.6321</f>
+        <f>$B23+-0.6953</f>
         <v/>
       </c>
     </row>
@@ -3939,19 +3946,19 @@
         <v/>
       </c>
       <c r="E24">
-        <f>$B24+0.9865</f>
+        <f>$B24+0.7763</f>
         <v/>
       </c>
       <c r="F24">
-        <f>$B24+-0.4399</f>
+        <f>$B24+-0.2781</f>
         <v/>
       </c>
       <c r="G24">
-        <f>$B24+0.5938</f>
+        <f>$B24+0.6532</f>
         <v/>
       </c>
       <c r="H24">
-        <f>$B24+-0.5938</f>
+        <f>$B24+-0.6532</f>
         <v/>
       </c>
     </row>
@@ -3972,19 +3979,19 @@
         <v/>
       </c>
       <c r="E25">
-        <f>$B25+1.0358</f>
+        <f>$B25+0.8247</f>
         <v/>
       </c>
       <c r="F25">
-        <f>$B25+-0.486</f>
+        <f>$B25+-0.3248</f>
         <v/>
       </c>
       <c r="G25">
-        <f>$B25+0.5578</f>
+        <f>$B25+0.6136</f>
         <v/>
       </c>
       <c r="H25">
-        <f>$B25+-0.5578</f>
+        <f>$B25+-0.6136</f>
         <v/>
       </c>
     </row>
@@ -4005,19 +4012,19 @@
         <v/>
       </c>
       <c r="E26">
-        <f>$B26+1.0821</f>
+        <f>$B26+0.8702</f>
         <v/>
       </c>
       <c r="F26">
-        <f>$B26+-0.5292</f>
+        <f>$B26+-0.3688</f>
         <v/>
       </c>
       <c r="G26">
-        <f>$B26+0.524</f>
+        <f>$B26+0.5764</f>
         <v/>
       </c>
       <c r="H26">
-        <f>$B26+-0.524</f>
+        <f>$B26+-0.5764</f>
         <v/>
       </c>
     </row>
@@ -4038,19 +4045,19 @@
         <v/>
       </c>
       <c r="E27">
-        <f>$B27+1.1256</f>
+        <f>$B27+0.9129</f>
         <v/>
       </c>
       <c r="F27">
-        <f>$B27+-0.5699</f>
+        <f>$B27+-0.41</f>
         <v/>
       </c>
       <c r="G27">
-        <f>$B27+0.4923</f>
+        <f>$B27+0.5415</f>
         <v/>
       </c>
       <c r="H27">
-        <f>$B27+-0.4923</f>
+        <f>$B27+-0.5415</f>
         <v/>
       </c>
     </row>
@@ -4071,19 +4078,19 @@
         <v/>
       </c>
       <c r="E28">
-        <f>$B28+1.1664</f>
+        <f>$B28+0.953</f>
         <v/>
       </c>
       <c r="F28">
-        <f>$B28+-0.6081</f>
+        <f>$B28+-0.4488</f>
         <v/>
       </c>
       <c r="G28">
-        <f>$B28+0.4625</f>
+        <f>$B28+0.5087</f>
         <v/>
       </c>
       <c r="H28">
-        <f>$B28+-0.4625</f>
+        <f>$B28+-0.5087</f>
         <v/>
       </c>
     </row>
@@ -4104,19 +4111,19 @@
         <v/>
       </c>
       <c r="E29">
-        <f>$B29+1.2048</f>
+        <f>$B29+0.9907</f>
         <v/>
       </c>
       <c r="F29">
-        <f>$B29+-0.6439</f>
+        <f>$B29+-0.4852</f>
         <v/>
       </c>
       <c r="G29">
-        <f>$B29+0.4344</f>
+        <f>$B29+0.4779</f>
         <v/>
       </c>
       <c r="H29">
-        <f>$B29+-0.4344</f>
+        <f>$B29+-0.4779</f>
         <v/>
       </c>
     </row>
@@ -4137,19 +4144,19 @@
         <v/>
       </c>
       <c r="E30">
-        <f>$B30+1.2409</f>
+        <f>$B30+1.0261</f>
         <v/>
       </c>
       <c r="F30">
-        <f>$B30+-0.6776</f>
+        <f>$B30+-0.5195</f>
         <v/>
       </c>
       <c r="G30">
-        <f>$B30+0.4081</f>
+        <f>$B30+0.4489</f>
         <v/>
       </c>
       <c r="H30">
-        <f>$B30+-0.4081</f>
+        <f>$B30+-0.4489</f>
         <v/>
       </c>
     </row>
@@ -4170,19 +4177,19 @@
         <v/>
       </c>
       <c r="E31">
-        <f>$B31+1.2748</f>
+        <f>$B31+1.0593</f>
         <v/>
       </c>
       <c r="F31">
-        <f>$B31+-0.7093</f>
+        <f>$B31+-0.5516</f>
         <v/>
       </c>
       <c r="G31">
-        <f>$B31+0.3834</f>
+        <f>$B31+0.4217</f>
         <v/>
       </c>
       <c r="H31">
-        <f>$B31+-0.3834</f>
+        <f>$B31+-0.4217</f>
         <v/>
       </c>
     </row>
@@ -4203,19 +4210,19 @@
         <v/>
       </c>
       <c r="E32">
-        <f>$B32+1.3066</f>
+        <f>$B32+1.0906</f>
         <v/>
       </c>
       <c r="F32">
-        <f>$B32+-0.739</f>
+        <f>$B32+-0.5818</f>
         <v/>
       </c>
       <c r="G32">
-        <f>$B32+0.3602</f>
+        <f>$B32+0.3962</f>
         <v/>
       </c>
       <c r="H32">
-        <f>$B32+-0.3602</f>
+        <f>$B32+-0.3962</f>
         <v/>
       </c>
     </row>
@@ -4236,19 +4243,19 @@
         <v/>
       </c>
       <c r="E33">
-        <f>$B33+1.3365</f>
+        <f>$B33+1.1199</f>
         <v/>
       </c>
       <c r="F33">
-        <f>$B33+-0.7669</f>
+        <f>$B33+-0.6102</f>
         <v/>
       </c>
       <c r="G33">
-        <f>$B33+0.3383</f>
+        <f>$B33+0.3722</f>
         <v/>
       </c>
       <c r="H33">
-        <f>$B33+-0.3383</f>
+        <f>$B33+-0.3722</f>
         <v/>
       </c>
     </row>
@@ -4269,19 +4276,19 @@
         <v/>
       </c>
       <c r="E34">
-        <f>$B34+1.3646</f>
+        <f>$B34+1.1475</f>
         <v/>
       </c>
       <c r="F34">
-        <f>$B34+-0.7932</f>
+        <f>$B34+-0.6368</f>
         <v/>
       </c>
       <c r="G34">
-        <f>$B34+0.3178</f>
+        <f>$B34+0.3496</f>
         <v/>
       </c>
       <c r="H34">
-        <f>$B34+-0.3178</f>
+        <f>$B34+-0.3496</f>
         <v/>
       </c>
     </row>
@@ -4302,19 +4309,19 @@
         <v/>
       </c>
       <c r="E35">
-        <f>$B35+1.3909</f>
+        <f>$B35+1.1734</f>
         <v/>
       </c>
       <c r="F35">
-        <f>$B35+-0.8178</f>
+        <f>$B35+-0.6618</f>
         <v/>
       </c>
       <c r="G35">
-        <f>$B35+0.2986</f>
+        <f>$B35+0.3284</f>
         <v/>
       </c>
       <c r="H35">
-        <f>$B35+-0.2986</f>
+        <f>$B35+-0.3284</f>
         <v/>
       </c>
     </row>
@@ -4335,19 +4342,19 @@
         <v/>
       </c>
       <c r="E36">
-        <f>$B36+1.4157</f>
+        <f>$B36+1.1977</f>
         <v/>
       </c>
       <c r="F36">
-        <f>$B36+-0.841</f>
+        <f>$B36+-0.6854</f>
         <v/>
       </c>
       <c r="G36">
-        <f>$B36+0.2805</f>
+        <f>$B36+0.3085</f>
         <v/>
       </c>
       <c r="H36">
-        <f>$B36+-0.2805</f>
+        <f>$B36+-0.3085</f>
         <v/>
       </c>
     </row>
@@ -4368,19 +4375,19 @@
         <v/>
       </c>
       <c r="E37">
-        <f>$B37+1.439</f>
+        <f>$B37+1.2206</f>
         <v/>
       </c>
       <c r="F37">
-        <f>$B37+-0.8627</f>
+        <f>$B37+-0.7075</f>
         <v/>
       </c>
       <c r="G37">
-        <f>$B37+0.2635</f>
+        <f>$B37+0.2898</f>
         <v/>
       </c>
       <c r="H37">
-        <f>$B37+-0.2635</f>
+        <f>$B37+-0.2898</f>
         <v/>
       </c>
     </row>
@@ -4401,19 +4408,19 @@
         <v/>
       </c>
       <c r="E38">
-        <f>$B38+1.4609</f>
+        <f>$B38+1.2421</f>
         <v/>
       </c>
       <c r="F38">
-        <f>$B38+-0.8832</f>
+        <f>$B38+-0.7282</f>
         <v/>
       </c>
       <c r="G38">
-        <f>$B38+0.2475</f>
+        <f>$B38+0.2723</f>
         <v/>
       </c>
       <c r="H38">
-        <f>$B38+-0.2475</f>
+        <f>$B38+-0.2723</f>
         <v/>
       </c>
     </row>
@@ -4434,19 +4441,19 @@
         <v/>
       </c>
       <c r="E39">
-        <f>$B39+1.4814</f>
+        <f>$B39+1.2622</f>
         <v/>
       </c>
       <c r="F39">
-        <f>$B39+-0.9024</f>
+        <f>$B39+-0.7477</f>
         <v/>
       </c>
       <c r="G39">
-        <f>$B39+0.2325</f>
+        <f>$B39+0.2558</f>
         <v/>
       </c>
       <c r="H39">
-        <f>$B39+-0.2325</f>
+        <f>$B39+-0.2558</f>
         <v/>
       </c>
     </row>
@@ -4467,19 +4474,19 @@
         <v/>
       </c>
       <c r="E40">
-        <f>$B40+1.5007</f>
+        <f>$B40+1.2812</f>
         <v/>
       </c>
       <c r="F40">
-        <f>$B40+-0.9204</f>
+        <f>$B40+-0.766</f>
         <v/>
       </c>
       <c r="G40">
-        <f>$B40+0.2184</f>
+        <f>$B40+0.2403</f>
         <v/>
       </c>
       <c r="H40">
-        <f>$B40+-0.2184</f>
+        <f>$B40+-0.2403</f>
         <v/>
       </c>
     </row>
@@ -4500,19 +4507,19 @@
         <v/>
       </c>
       <c r="E41">
-        <f>$B41+1.5189</f>
+        <f>$B41+1.299</f>
         <v/>
       </c>
       <c r="F41">
-        <f>$B41+-0.9373</f>
+        <f>$B41+-0.7832</f>
         <v/>
       </c>
       <c r="G41">
-        <f>$B41+0.2052</f>
+        <f>$B41+0.2257</f>
         <v/>
       </c>
       <c r="H41">
-        <f>$B41+-0.2052</f>
+        <f>$B41+-0.2257</f>
         <v/>
       </c>
     </row>
@@ -4533,19 +4540,19 @@
         <v/>
       </c>
       <c r="E42">
-        <f>$B42+1.5359</f>
+        <f>$B42+1.3157</f>
         <v/>
       </c>
       <c r="F42">
-        <f>$B42+-0.9532</f>
+        <f>$B42+-0.7994</f>
         <v/>
       </c>
       <c r="G42">
-        <f>$B42+0.1928</f>
+        <f>$B42+0.2121</f>
         <v/>
       </c>
       <c r="H42">
-        <f>$B42+-0.1928</f>
+        <f>$B42+-0.2121</f>
         <v/>
       </c>
     </row>
@@ -4566,19 +4573,19 @@
         <v/>
       </c>
       <c r="E43">
-        <f>$B43+1.5519</f>
+        <f>$B43+1.3314</f>
         <v/>
       </c>
       <c r="F43">
-        <f>$B43+-0.9682</f>
+        <f>$B43+-0.8146</f>
         <v/>
       </c>
       <c r="G43">
-        <f>$B43+0.1811</f>
+        <f>$B43+0.1992</f>
         <v/>
       </c>
       <c r="H43">
-        <f>$B43+-0.1811</f>
+        <f>$B43+-0.1992</f>
         <v/>
       </c>
     </row>
@@ -4599,19 +4606,19 @@
         <v/>
       </c>
       <c r="E44">
-        <f>$B44+1.5669</f>
+        <f>$B44+1.3462</f>
         <v/>
       </c>
       <c r="F44">
-        <f>$B44+-0.9822</f>
+        <f>$B44+-0.8288</f>
         <v/>
       </c>
       <c r="G44">
-        <f>$B44+0.1701</f>
+        <f>$B44+0.1871</f>
         <v/>
       </c>
       <c r="H44">
-        <f>$B44+-0.1701</f>
+        <f>$B44+-0.1871</f>
         <v/>
       </c>
     </row>
@@ -4632,19 +4639,19 @@
         <v/>
       </c>
       <c r="E45">
-        <f>$B45+1.581</f>
+        <f>$B45+1.36</f>
         <v/>
       </c>
       <c r="F45">
-        <f>$B45+-0.9954</f>
+        <f>$B45+-0.8422</f>
         <v/>
       </c>
       <c r="G45">
-        <f>$B45+0.1598</f>
+        <f>$B45+0.1758</f>
         <v/>
       </c>
       <c r="H45">
-        <f>$B45+-0.1598</f>
+        <f>$B45+-0.1758</f>
         <v/>
       </c>
     </row>
@@ -4665,19 +4672,19 @@
         <v/>
       </c>
       <c r="E46">
-        <f>$B46+1.5943</f>
+        <f>$B46+1.3731</f>
         <v/>
       </c>
       <c r="F46">
-        <f>$B46+-1.0078</f>
+        <f>$B46+-0.8548</f>
         <v/>
       </c>
       <c r="G46">
-        <f>$B46+0.1501</f>
+        <f>$B46+0.1652</f>
         <v/>
       </c>
       <c r="H46">
-        <f>$B46+-0.1501</f>
+        <f>$B46+-0.1652</f>
         <v/>
       </c>
     </row>
@@ -4698,19 +4705,19 @@
         <v/>
       </c>
       <c r="E47">
-        <f>$B47+1.6068</f>
+        <f>$B47+1.3853</f>
         <v/>
       </c>
       <c r="F47">
-        <f>$B47+-1.0195</f>
+        <f>$B47+-0.8666</f>
         <v/>
       </c>
       <c r="G47">
-        <f>$B47+0.141</f>
+        <f>$B47+0.1551</f>
         <v/>
       </c>
       <c r="H47">
-        <f>$B47+-0.141</f>
+        <f>$B47+-0.1551</f>
         <v/>
       </c>
     </row>
@@ -4731,19 +4738,19 @@
         <v/>
       </c>
       <c r="E48">
-        <f>$B48+1.6185</f>
+        <f>$B48+1.3968</f>
         <v/>
       </c>
       <c r="F48">
-        <f>$B48+-1.0304</f>
+        <f>$B48+-0.8778</f>
         <v/>
       </c>
       <c r="G48">
-        <f>$B48+0.1325</f>
+        <f>$B48+0.1457</f>
         <v/>
       </c>
       <c r="H48">
-        <f>$B48+-0.1325</f>
+        <f>$B48+-0.1457</f>
         <v/>
       </c>
     </row>
@@ -4764,19 +4771,19 @@
         <v/>
       </c>
       <c r="E49">
-        <f>$B49+1.6295</f>
+        <f>$B49+1.4076</f>
         <v/>
       </c>
       <c r="F49">
-        <f>$B49+-1.0407</f>
+        <f>$B49+-0.8882</f>
         <v/>
       </c>
       <c r="G49">
-        <f>$B49+0.1245</f>
+        <f>$B49+0.1369</f>
         <v/>
       </c>
       <c r="H49">
-        <f>$B49+-0.1245</f>
+        <f>$B49+-0.1369</f>
         <v/>
       </c>
     </row>
@@ -4797,19 +4804,19 @@
         <v/>
       </c>
       <c r="E50">
-        <f>$B50+1.6398</f>
+        <f>$B50+1.4177</f>
         <v/>
       </c>
       <c r="F50">
-        <f>$B50+-1.0503</f>
+        <f>$B50+-0.898</f>
         <v/>
       </c>
       <c r="G50">
-        <f>$B50+0.1169</f>
+        <f>$B50+0.1286</f>
         <v/>
       </c>
       <c r="H50">
-        <f>$B50+-0.1169</f>
+        <f>$B50+-0.1286</f>
         <v/>
       </c>
     </row>
@@ -4830,19 +4837,19 @@
         <v/>
       </c>
       <c r="E51">
-        <f>$B51+1.6495</f>
+        <f>$B51+1.4273</f>
         <v/>
       </c>
       <c r="F51">
-        <f>$B51+-1.0594</f>
+        <f>$B51+-0.9072</f>
         <v/>
       </c>
       <c r="G51">
-        <f>$B51+0.1098</f>
+        <f>$B51+0.1208</f>
         <v/>
       </c>
       <c r="H51">
-        <f>$B51+-0.1098</f>
+        <f>$B51+-0.1208</f>
         <v/>
       </c>
     </row>
@@ -4863,19 +4870,19 @@
         <v/>
       </c>
       <c r="E52">
-        <f>$B52+1.6586</f>
+        <f>$B52+1.4362</f>
         <v/>
       </c>
       <c r="F52">
-        <f>$B52+-1.0679</f>
+        <f>$B52+-0.9159</f>
         <v/>
       </c>
       <c r="G52">
-        <f>$B52+0.1032</f>
+        <f>$B52+0.1135</f>
         <v/>
       </c>
       <c r="H52">
-        <f>$B52+-0.1032</f>
+        <f>$B52+-0.1135</f>
         <v/>
       </c>
     </row>
@@ -4896,19 +4903,19 @@
         <v/>
       </c>
       <c r="E53">
-        <f>$B53+1.6672</f>
+        <f>$B53+1.4446</f>
         <v/>
       </c>
       <c r="F53">
-        <f>$B53+-1.0759</f>
+        <f>$B53+-0.924</f>
         <v/>
       </c>
       <c r="G53">
-        <f>$B53+0.0969</f>
+        <f>$B53+0.1066</f>
         <v/>
       </c>
       <c r="H53">
-        <f>$B53+-0.0969</f>
+        <f>$B53+-0.1066</f>
         <v/>
       </c>
     </row>
@@ -4929,19 +4936,19 @@
         <v/>
       </c>
       <c r="E54">
-        <f>$B54+1.6752</f>
+        <f>$B54+1.4525</f>
         <v/>
       </c>
       <c r="F54">
-        <f>$B54+-1.0834</f>
+        <f>$B54+-0.9316</f>
         <v/>
       </c>
       <c r="G54">
-        <f>$B54+0.0911</f>
+        <f>$B54+0.1002</f>
         <v/>
       </c>
       <c r="H54">
-        <f>$B54+-0.0911</f>
+        <f>$B54+-0.1002</f>
         <v/>
       </c>
     </row>
@@ -4962,19 +4969,19 @@
         <v/>
       </c>
       <c r="E55">
-        <f>$B55+1.6828</f>
+        <f>$B55+1.4599</f>
         <v/>
       </c>
       <c r="F55">
-        <f>$B55+-1.0905</f>
+        <f>$B55+-0.9388</f>
         <v/>
       </c>
       <c r="G55">
-        <f>$B55+0.0855</f>
+        <f>$B55+0.0941</f>
         <v/>
       </c>
       <c r="H55">
-        <f>$B55+-0.0855</f>
+        <f>$B55+-0.0941</f>
         <v/>
       </c>
     </row>
@@ -4995,19 +5002,19 @@
         <v/>
       </c>
       <c r="E56">
-        <f>$B56+1.6899</f>
+        <f>$B56+1.4669</f>
         <v/>
       </c>
       <c r="F56">
-        <f>$B56+-1.0971</f>
+        <f>$B56+-0.9455</f>
         <v/>
       </c>
       <c r="G56">
-        <f>$B56+0.0804</f>
+        <f>$B56+0.0884</f>
         <v/>
       </c>
       <c r="H56">
-        <f>$B56+-0.0804</f>
+        <f>$B56+-0.0884</f>
         <v/>
       </c>
     </row>
@@ -5028,19 +5035,19 @@
         <v/>
       </c>
       <c r="E57">
-        <f>$B57+1.6966</f>
+        <f>$B57+1.4735</f>
         <v/>
       </c>
       <c r="F57">
-        <f>$B57+-1.1034</f>
+        <f>$B57+-0.9519</f>
         <v/>
       </c>
       <c r="G57">
-        <f>$B57+0.0755</f>
+        <f>$B57+0.083</f>
         <v/>
       </c>
       <c r="H57">
-        <f>$B57+-0.0755</f>
+        <f>$B57+-0.083</f>
         <v/>
       </c>
     </row>
@@ -5061,19 +5068,19 @@
         <v/>
       </c>
       <c r="E58">
-        <f>$B58+1.7028</f>
+        <f>$B58+1.4796</f>
         <v/>
       </c>
       <c r="F58">
-        <f>$B58+-1.1092</f>
+        <f>$B58+-0.9578</f>
         <v/>
       </c>
       <c r="G58">
-        <f>$B58+0.0709</f>
+        <f>$B58+0.078</f>
         <v/>
       </c>
       <c r="H58">
-        <f>$B58+-0.0709</f>
+        <f>$B58+-0.078</f>
         <v/>
       </c>
     </row>
@@ -5094,19 +5101,19 @@
         <v/>
       </c>
       <c r="E59">
-        <f>$B59+1.7087</f>
+        <f>$B59+1.4854</f>
         <v/>
       </c>
       <c r="F59">
-        <f>$B59+-1.1147</f>
+        <f>$B59+-0.9634</f>
         <v/>
       </c>
       <c r="G59">
-        <f>$B59+0.0666</f>
+        <f>$B59+0.0733</f>
         <v/>
       </c>
       <c r="H59">
-        <f>$B59+-0.0666</f>
+        <f>$B59+-0.0733</f>
         <v/>
       </c>
     </row>
@@ -5127,19 +5134,19 @@
         <v/>
       </c>
       <c r="E60">
-        <f>$B60+1.7143</f>
+        <f>$B60+1.4908</f>
         <v/>
       </c>
       <c r="F60">
-        <f>$B60+-1.1199</f>
+        <f>$B60+-0.9686</f>
         <v/>
       </c>
       <c r="G60">
-        <f>$B60+0.0626</f>
+        <f>$B60+0.0688</f>
         <v/>
       </c>
       <c r="H60">
-        <f>$B60+-0.0626</f>
+        <f>$B60+-0.0688</f>
         <v/>
       </c>
     </row>
@@ -5160,19 +5167,19 @@
         <v/>
       </c>
       <c r="E61">
-        <f>$B61+1.7195</f>
+        <f>$B61+1.4959</f>
         <v/>
       </c>
       <c r="F61">
-        <f>$B61+-1.1247</f>
+        <f>$B61+-0.9736</f>
         <v/>
       </c>
       <c r="G61">
-        <f>$B61+0.0588</f>
+        <f>$B61+0.0647</f>
         <v/>
       </c>
       <c r="H61">
-        <f>$B61+-0.0588</f>
+        <f>$B61+-0.0647</f>
         <v/>
       </c>
     </row>
@@ -5193,19 +5200,19 @@
         <v/>
       </c>
       <c r="E62">
-        <f>$B62+1.7243</f>
+        <f>$B62+1.5007</f>
         <v/>
       </c>
       <c r="F62">
-        <f>$B62+-1.1293</f>
+        <f>$B62+-0.9782</f>
         <v/>
       </c>
       <c r="G62">
-        <f>$B62+0.0552</f>
+        <f>$B62+0.0608</f>
         <v/>
       </c>
       <c r="H62">
-        <f>$B62+-0.0552</f>
+        <f>$B62+-0.0608</f>
         <v/>
       </c>
     </row>
@@ -5226,19 +5233,19 @@
         <v/>
       </c>
       <c r="E63">
-        <f>$B63+1.7289</f>
+        <f>$B63+1.5052</f>
         <v/>
       </c>
       <c r="F63">
-        <f>$B63+-1.1336</f>
+        <f>$B63+-0.9825</f>
         <v/>
       </c>
       <c r="G63">
-        <f>$B63+0.0519</f>
+        <f>$B63+0.0571</f>
         <v/>
       </c>
       <c r="H63">
-        <f>$B63+-0.0519</f>
+        <f>$B63+-0.0571</f>
         <v/>
       </c>
     </row>
@@ -5259,19 +5266,19 @@
         <v/>
       </c>
       <c r="E64">
-        <f>$B64+1.7332</f>
+        <f>$B64+1.5094</f>
         <v/>
       </c>
       <c r="F64">
-        <f>$B64+-1.1376</f>
+        <f>$B64+-0.9866</f>
         <v/>
       </c>
       <c r="G64">
-        <f>$B64+0.0487</f>
+        <f>$B64+0.0536</f>
         <v/>
       </c>
       <c r="H64">
-        <f>$B64+-0.0487</f>
+        <f>$B64+-0.0536</f>
         <v/>
       </c>
     </row>
@@ -5292,19 +5299,19 @@
         <v/>
       </c>
       <c r="E65">
-        <f>$B65+1.7373</f>
+        <f>$B65+1.5134</f>
         <v/>
       </c>
       <c r="F65">
-        <f>$B65+-1.1414</f>
+        <f>$B65+-0.9905</f>
         <v/>
       </c>
       <c r="G65">
-        <f>$B65+0.0458</f>
+        <f>$B65+0.0504</f>
         <v/>
       </c>
       <c r="H65">
-        <f>$B65+-0.0458</f>
+        <f>$B65+-0.0504</f>
         <v/>
       </c>
     </row>
@@ -5325,19 +5332,19 @@
         <v/>
       </c>
       <c r="E66">
-        <f>$B66+1.7411</f>
+        <f>$B66+1.5171</f>
         <v/>
       </c>
       <c r="F66">
-        <f>$B66+-1.1449</f>
+        <f>$B66+-0.9941</f>
         <v/>
       </c>
       <c r="G66">
-        <f>$B66+0.043</f>
+        <f>$B66+0.0473</f>
         <v/>
       </c>
       <c r="H66">
-        <f>$B66+-0.043</f>
+        <f>$B66+-0.0473</f>
         <v/>
       </c>
     </row>
@@ -5358,19 +5365,19 @@
         <v/>
       </c>
       <c r="E67">
-        <f>$B67+1.7446</f>
+        <f>$B67+1.5207</f>
         <v/>
       </c>
       <c r="F67">
-        <f>$B67+-1.1483</f>
+        <f>$B67+-0.9975</f>
         <v/>
       </c>
       <c r="G67">
-        <f>$B67+0.0404</f>
+        <f>$B67+0.0444</f>
         <v/>
       </c>
       <c r="H67">
-        <f>$B67+-0.0404</f>
+        <f>$B67+-0.0444</f>
         <v/>
       </c>
     </row>
@@ -5391,19 +5398,19 @@
         <v/>
       </c>
       <c r="E68">
-        <f>$B68+1.748</f>
+        <f>$B68+1.5239</f>
         <v/>
       </c>
       <c r="F68">
-        <f>$B68+-1.1514</f>
+        <f>$B68+-1.0007</f>
         <v/>
       </c>
       <c r="G68">
-        <f>$B68+0.038</f>
+        <f>$B68+0.0418</f>
         <v/>
       </c>
       <c r="H68">
-        <f>$B68+-0.038</f>
+        <f>$B68+-0.0418</f>
         <v/>
       </c>
     </row>
@@ -5424,19 +5431,19 @@
         <v/>
       </c>
       <c r="E69">
-        <f>$B69+1.7511</f>
+        <f>$B69+1.527</f>
         <v/>
       </c>
       <c r="F69">
-        <f>$B69+-1.1544</f>
+        <f>$B69+-1.0036</f>
         <v/>
       </c>
       <c r="G69">
-        <f>$B69+0.0357</f>
+        <f>$B69+0.0392</f>
         <v/>
       </c>
       <c r="H69">
-        <f>$B69+-0.0357</f>
+        <f>$B69+-0.0392</f>
         <v/>
       </c>
     </row>
@@ -5457,19 +5464,19 @@
         <v/>
       </c>
       <c r="E70">
-        <f>$B70+1.7541</f>
+        <f>$B70+1.5299</f>
         <v/>
       </c>
       <c r="F70">
-        <f>$B70+-1.1571</f>
+        <f>$B70+-1.0064</f>
         <v/>
       </c>
       <c r="G70">
-        <f>$B70+0.0335</f>
+        <f>$B70+0.0369</f>
         <v/>
       </c>
       <c r="H70">
-        <f>$B70+-0.0335</f>
+        <f>$B70+-0.0369</f>
         <v/>
       </c>
     </row>
@@ -5490,19 +5497,19 @@
         <v/>
       </c>
       <c r="E71">
-        <f>$B71+1.7569</f>
+        <f>$B71+1.5327</f>
         <v/>
       </c>
       <c r="F71">
-        <f>$B71+-1.1597</f>
+        <f>$B71+-1.0091</f>
         <v/>
       </c>
       <c r="G71">
-        <f>$B71+0.0315</f>
+        <f>$B71+0.0346</f>
         <v/>
       </c>
       <c r="H71">
-        <f>$B71+-0.0315</f>
+        <f>$B71+-0.0346</f>
         <v/>
       </c>
     </row>
@@ -5523,19 +5530,19 @@
         <v/>
       </c>
       <c r="E72">
-        <f>$B72+1.7595</f>
+        <f>$B72+1.5352</f>
         <v/>
       </c>
       <c r="F72">
-        <f>$B72+-1.1622</f>
+        <f>$B72+-1.0116</f>
         <v/>
       </c>
       <c r="G72">
-        <f>$B72+0.0296</f>
+        <f>$B72+0.0325</f>
         <v/>
       </c>
       <c r="H72">
-        <f>$B72+-0.0296</f>
+        <f>$B72+-0.0325</f>
         <v/>
       </c>
     </row>
@@ -5556,19 +5563,19 @@
         <v/>
       </c>
       <c r="E73">
-        <f>$B73+1.762</f>
+        <f>$B73+1.5376</f>
         <v/>
       </c>
       <c r="F73">
-        <f>$B73+-1.1645</f>
+        <f>$B73+-1.0139</f>
         <v/>
       </c>
       <c r="G73">
-        <f>$B73+0.0278</f>
+        <f>$B73+0.0305</f>
         <v/>
       </c>
       <c r="H73">
-        <f>$B73+-0.0278</f>
+        <f>$B73+-0.0305</f>
         <v/>
       </c>
     </row>
@@ -5589,19 +5596,19 @@
         <v/>
       </c>
       <c r="E74">
-        <f>$B74+1.7643</f>
+        <f>$B74+1.5399</f>
         <v/>
       </c>
       <c r="F74">
-        <f>$B74+-1.1666</f>
+        <f>$B74+-1.0161</f>
         <v/>
       </c>
       <c r="G74">
-        <f>$B74+0.0261</f>
+        <f>$B74+0.0287</f>
         <v/>
       </c>
       <c r="H74">
-        <f>$B74+-0.0261</f>
+        <f>$B74+-0.0287</f>
         <v/>
       </c>
     </row>
@@ -5622,19 +5629,19 @@
         <v/>
       </c>
       <c r="E75">
-        <f>$B75+1.7664</f>
+        <f>$B75+1.542</f>
         <v/>
       </c>
       <c r="F75">
-        <f>$B75+-1.1686</f>
+        <f>$B75+-1.0181</f>
         <v/>
       </c>
       <c r="G75">
-        <f>$B75+0.0245</f>
+        <f>$B75+0.027</f>
         <v/>
       </c>
       <c r="H75">
-        <f>$B75+-0.0245</f>
+        <f>$B75+-0.027</f>
         <v/>
       </c>
     </row>
@@ -5655,19 +5662,19 @@
         <v/>
       </c>
       <c r="E76">
-        <f>$B76+1.7685</f>
+        <f>$B76+1.544</f>
         <v/>
       </c>
       <c r="F76">
-        <f>$B76+-1.1705</f>
+        <f>$B76+-1.0201</f>
         <v/>
       </c>
       <c r="G76">
-        <f>$B76+0.023</f>
+        <f>$B76+0.0253</f>
         <v/>
       </c>
       <c r="H76">
-        <f>$B76+-0.023</f>
+        <f>$B76+-0.0253</f>
         <v/>
       </c>
     </row>
@@ -5688,19 +5695,19 @@
         <v/>
       </c>
       <c r="E77">
-        <f>$B77+1.7704</f>
+        <f>$B77+1.5459</f>
         <v/>
       </c>
       <c r="F77">
-        <f>$B77+-1.1723</f>
+        <f>$B77+-1.0219</f>
         <v/>
       </c>
       <c r="G77">
-        <f>$B77+0.0216</f>
+        <f>$B77+0.0238</f>
         <v/>
       </c>
       <c r="H77">
-        <f>$B77+-0.0216</f>
+        <f>$B77+-0.0238</f>
         <v/>
       </c>
     </row>
@@ -5721,19 +5728,19 @@
         <v/>
       </c>
       <c r="E78">
-        <f>$B78+1.7722</f>
+        <f>$B78+1.5477</f>
         <v/>
       </c>
       <c r="F78">
-        <f>$B78+-1.174</f>
+        <f>$B78+-1.0236</f>
         <v/>
       </c>
       <c r="G78">
-        <f>$B78+0.0203</f>
+        <f>$B78+0.0224</f>
         <v/>
       </c>
       <c r="H78">
-        <f>$B78+-0.0203</f>
+        <f>$B78+-0.0224</f>
         <v/>
       </c>
     </row>
@@ -5754,19 +5761,19 @@
         <v/>
       </c>
       <c r="E79">
-        <f>$B79+1.7738</f>
+        <f>$B79+1.5493</f>
         <v/>
       </c>
       <c r="F79">
-        <f>$B79+-1.1756</f>
+        <f>$B79+-1.0252</f>
         <v/>
       </c>
       <c r="G79">
-        <f>$B79+0.0191</f>
+        <f>$B79+0.021</f>
         <v/>
       </c>
       <c r="H79">
-        <f>$B79+-0.0191</f>
+        <f>$B79+-0.021</f>
         <v/>
       </c>
     </row>
@@ -5787,19 +5794,19 @@
         <v/>
       </c>
       <c r="E80">
-        <f>$B80+1.7754</f>
+        <f>$B80+1.5509</f>
         <v/>
       </c>
       <c r="F80">
-        <f>$B80+-1.177</f>
+        <f>$B80+-1.0267</f>
         <v/>
       </c>
       <c r="G80">
-        <f>$B80+0.0179</f>
+        <f>$B80+0.0197</f>
         <v/>
       </c>
       <c r="H80">
-        <f>$B80+-0.0179</f>
+        <f>$B80+-0.0197</f>
         <v/>
       </c>
     </row>
@@ -5820,19 +5827,19 @@
         <v/>
       </c>
       <c r="E81">
-        <f>$B81+1.7769</f>
+        <f>$B81+1.5523</f>
         <v/>
       </c>
       <c r="F81">
-        <f>$B81+-1.1784</f>
+        <f>$B81+-1.0281</f>
         <v/>
       </c>
       <c r="G81">
-        <f>$B81+0.0168</f>
+        <f>$B81+0.0185</f>
         <v/>
       </c>
       <c r="H81">
-        <f>$B81+-0.0168</f>
+        <f>$B81+-0.0185</f>
         <v/>
       </c>
     </row>
@@ -5853,19 +5860,19 @@
         <v/>
       </c>
       <c r="E82">
-        <f>$B82+1.7783</f>
+        <f>$B82+1.5537</f>
         <v/>
       </c>
       <c r="F82">
-        <f>$B82+-1.1797</f>
+        <f>$B82+-1.0294</f>
         <v/>
       </c>
       <c r="G82">
-        <f>$B82+0.0158</f>
+        <f>$B82+0.0174</f>
         <v/>
       </c>
       <c r="H82">
-        <f>$B82+-0.0158</f>
+        <f>$B82+-0.0174</f>
         <v/>
       </c>
     </row>
@@ -5886,19 +5893,19 @@
         <v/>
       </c>
       <c r="E83">
-        <f>$B83+1.7796</f>
+        <f>$B83+1.555</f>
         <v/>
       </c>
       <c r="F83">
-        <f>$B83+-1.181</f>
+        <f>$B83+-1.0307</f>
         <v/>
       </c>
       <c r="G83">
-        <f>$B83+0.0149</f>
+        <f>$B83+0.0164</f>
         <v/>
       </c>
       <c r="H83">
-        <f>$B83+-0.0149</f>
+        <f>$B83+-0.0164</f>
         <v/>
       </c>
     </row>
@@ -5919,19 +5926,19 @@
         <v/>
       </c>
       <c r="E84">
-        <f>$B84+1.7809</f>
+        <f>$B84+1.5562</f>
         <v/>
       </c>
       <c r="F84">
-        <f>$B84+-1.1821</f>
+        <f>$B84+-1.0318</f>
         <v/>
       </c>
       <c r="G84">
-        <f>$B84+0.014</f>
+        <f>$B84+0.0154</f>
         <v/>
       </c>
       <c r="H84">
-        <f>$B84+-0.014</f>
+        <f>$B84+-0.0154</f>
         <v/>
       </c>
     </row>
@@ -5952,19 +5959,19 @@
         <v/>
       </c>
       <c r="E85">
-        <f>$B85+1.782</f>
+        <f>$B85+1.5574</f>
         <v/>
       </c>
       <c r="F85">
-        <f>$B85+-1.1832</f>
+        <f>$B85+-1.0329</f>
         <v/>
       </c>
       <c r="G85">
-        <f>$B85+0.0131</f>
+        <f>$B85+0.0144</f>
         <v/>
       </c>
       <c r="H85">
-        <f>$B85+-0.0131</f>
+        <f>$B85+-0.0144</f>
         <v/>
       </c>
     </row>
@@ -5985,19 +5992,19 @@
         <v/>
       </c>
       <c r="E86">
-        <f>$B86+1.7831</f>
+        <f>$B86+1.5584</f>
         <v/>
       </c>
       <c r="F86">
-        <f>$B86+-1.1842</f>
+        <f>$B86+-1.034</f>
         <v/>
       </c>
       <c r="G86">
-        <f>$B86+0.0123</f>
+        <f>$B86+0.0136</f>
         <v/>
       </c>
       <c r="H86">
-        <f>$B86+-0.0123</f>
+        <f>$B86+-0.0136</f>
         <v/>
       </c>
     </row>
@@ -6018,19 +6025,19 @@
         <v/>
       </c>
       <c r="E87">
-        <f>$B87+1.7841</f>
+        <f>$B87+1.5594</f>
         <v/>
       </c>
       <c r="F87">
-        <f>$B87+-1.1852</f>
+        <f>$B87+-1.0349</f>
         <v/>
       </c>
       <c r="G87">
-        <f>$B87+0.0116</f>
+        <f>$B87+0.0127</f>
         <v/>
       </c>
       <c r="H87">
-        <f>$B87+-0.0116</f>
+        <f>$B87+-0.0127</f>
         <v/>
       </c>
     </row>
@@ -6051,19 +6058,19 @@
         <v/>
       </c>
       <c r="E88">
-        <f>$B88+1.7851</f>
+        <f>$B88+1.5604</f>
         <v/>
       </c>
       <c r="F88">
-        <f>$B88+-1.1861</f>
+        <f>$B88+-1.0359</f>
         <v/>
       </c>
       <c r="G88">
-        <f>$B88+0.0109</f>
+        <f>$B88+0.012</f>
         <v/>
       </c>
       <c r="H88">
-        <f>$B88+-0.0109</f>
+        <f>$B88+-0.012</f>
         <v/>
       </c>
     </row>
@@ -6084,19 +6091,19 @@
         <v/>
       </c>
       <c r="E89">
-        <f>$B89+1.786</f>
+        <f>$B89+1.5613</f>
         <v/>
       </c>
       <c r="F89">
-        <f>$B89+-1.1869</f>
+        <f>$B89+-1.0367</f>
         <v/>
       </c>
       <c r="G89">
-        <f>$B89+0.0102</f>
+        <f>$B89+0.0112</f>
         <v/>
       </c>
       <c r="H89">
-        <f>$B89+-0.0102</f>
+        <f>$B89+-0.0112</f>
         <v/>
       </c>
     </row>
@@ -6117,19 +6124,19 @@
         <v/>
       </c>
       <c r="E90">
-        <f>$B90+1.7869</f>
+        <f>$B90+1.5621</f>
         <v/>
       </c>
       <c r="F90">
-        <f>$B90+-1.1877</f>
+        <f>$B90+-1.0375</f>
         <v/>
       </c>
       <c r="G90">
-        <f>$B90+0.0096</f>
+        <f>$B90+0.0106</f>
         <v/>
       </c>
       <c r="H90">
-        <f>$B90+-0.0096</f>
+        <f>$B90+-0.0106</f>
         <v/>
       </c>
     </row>
@@ -6150,19 +6157,19 @@
         <v/>
       </c>
       <c r="E91">
-        <f>$B91+1.7876</f>
+        <f>$B91+1.5629</f>
         <v/>
       </c>
       <c r="F91">
-        <f>$B91+-1.1885</f>
+        <f>$B91+-1.0383</f>
         <v/>
       </c>
       <c r="G91">
-        <f>$B91+0.009</f>
+        <f>$B91+0.0099</f>
         <v/>
       </c>
       <c r="H91">
-        <f>$B91+-0.009</f>
+        <f>$B91+-0.0099</f>
         <v/>
       </c>
     </row>
@@ -6183,19 +6190,19 @@
         <v/>
       </c>
       <c r="E92">
-        <f>$B92+1.7884</f>
+        <f>$B92+1.5636</f>
         <v/>
       </c>
       <c r="F92">
-        <f>$B92+-1.1892</f>
+        <f>$B92+-1.039</f>
         <v/>
       </c>
       <c r="G92">
-        <f>$B92+0.0085</f>
+        <f>$B92+0.0093</f>
         <v/>
       </c>
       <c r="H92">
-        <f>$B92+-0.0085</f>
+        <f>$B92+-0.0093</f>
         <v/>
       </c>
     </row>
@@ -6216,19 +6223,19 @@
         <v/>
       </c>
       <c r="E93">
-        <f>$B93+1.7891</f>
+        <f>$B93+1.5643</f>
         <v/>
       </c>
       <c r="F93">
-        <f>$B93+-1.1898</f>
+        <f>$B93+-1.0397</f>
         <v/>
       </c>
       <c r="G93">
-        <f>$B93+0.008</f>
+        <f>$B93+0.0088</f>
         <v/>
       </c>
       <c r="H93">
-        <f>$B93+-0.008</f>
+        <f>$B93+-0.0088</f>
         <v/>
       </c>
     </row>
@@ -6249,19 +6256,19 @@
         <v/>
       </c>
       <c r="E94">
-        <f>$B94+1.7898</f>
+        <f>$B94+1.5649</f>
         <v/>
       </c>
       <c r="F94">
-        <f>$B94+-1.1904</f>
+        <f>$B94+-1.0403</f>
         <v/>
       </c>
       <c r="G94">
-        <f>$B94+0.0075</f>
+        <f>$B94+0.0082</f>
         <v/>
       </c>
       <c r="H94">
-        <f>$B94+-0.0075</f>
+        <f>$B94+-0.0082</f>
         <v/>
       </c>
     </row>
@@ -6282,19 +6289,19 @@
         <v/>
       </c>
       <c r="E95">
-        <f>$B95+1.7904</f>
+        <f>$B95+1.5656</f>
         <v/>
       </c>
       <c r="F95">
-        <f>$B95+-1.191</f>
+        <f>$B95+-1.0409</f>
         <v/>
       </c>
       <c r="G95">
-        <f>$B95+0.007</f>
+        <f>$B95+0.0077</f>
         <v/>
       </c>
       <c r="H95">
-        <f>$B95+-0.007</f>
+        <f>$B95+-0.0077</f>
         <v/>
       </c>
     </row>
@@ -6315,19 +6322,19 @@
         <v/>
       </c>
       <c r="E96">
-        <f>$B96+1.791</f>
+        <f>$B96+1.5661</f>
         <v/>
       </c>
       <c r="F96">
-        <f>$B96+-1.1916</f>
+        <f>$B96+-1.0414</f>
         <v/>
       </c>
       <c r="G96">
-        <f>$B96+0.0066</f>
+        <f>$B96+0.0073</f>
         <v/>
       </c>
       <c r="H96">
-        <f>$B96+-0.0066</f>
+        <f>$B96+-0.0073</f>
         <v/>
       </c>
     </row>
@@ -6348,19 +6355,19 @@
         <v/>
       </c>
       <c r="E97">
-        <f>$B97+1.7915</f>
+        <f>$B97+1.5667</f>
         <v/>
       </c>
       <c r="F97">
-        <f>$B97+-1.1921</f>
+        <f>$B97+-1.0419</f>
         <v/>
       </c>
       <c r="G97">
-        <f>$B97+0.0062</f>
+        <f>$B97+0.0068</f>
         <v/>
       </c>
       <c r="H97">
-        <f>$B97+-0.0062</f>
+        <f>$B97+-0.0068</f>
         <v/>
       </c>
     </row>
@@ -6381,19 +6388,19 @@
         <v/>
       </c>
       <c r="E98">
-        <f>$B98+1.792</f>
+        <f>$B98+1.5672</f>
         <v/>
       </c>
       <c r="F98">
-        <f>$B98+-1.1925</f>
+        <f>$B98+-1.0424</f>
         <v/>
       </c>
       <c r="G98">
-        <f>$B98+0.0058</f>
+        <f>$B98+0.0064</f>
         <v/>
       </c>
       <c r="H98">
-        <f>$B98+-0.0058</f>
+        <f>$B98+-0.0064</f>
         <v/>
       </c>
     </row>
@@ -6414,19 +6421,19 @@
         <v/>
       </c>
       <c r="E99">
-        <f>$B99+1.7925</f>
+        <f>$B99+1.5676</f>
         <v/>
       </c>
       <c r="F99">
-        <f>$B99+-1.193</f>
+        <f>$B99+-1.0429</f>
         <v/>
       </c>
       <c r="G99">
-        <f>$B99+0.0055</f>
+        <f>$B99+0.006</f>
         <v/>
       </c>
       <c r="H99">
-        <f>$B99+-0.0055</f>
+        <f>$B99+-0.006</f>
         <v/>
       </c>
     </row>
@@ -6447,19 +6454,19 @@
         <v/>
       </c>
       <c r="E100">
-        <f>$B100+1.793</f>
+        <f>$B100+1.5681</f>
         <v/>
       </c>
       <c r="F100">
-        <f>$B100+-1.1934</f>
+        <f>$B100+-1.0433</f>
         <v/>
       </c>
       <c r="G100">
-        <f>$B100+0.0051</f>
+        <f>$B100+0.0057</f>
         <v/>
       </c>
       <c r="H100">
-        <f>$B100+-0.0051</f>
+        <f>$B100+-0.0057</f>
         <v/>
       </c>
     </row>
@@ -6480,19 +6487,19 @@
         <v/>
       </c>
       <c r="E101">
-        <f>$B101+1.7934</f>
+        <f>$B101+1.5685</f>
         <v/>
       </c>
       <c r="F101">
-        <f>$B101+-1.1938</f>
+        <f>$B101+-1.0437</f>
         <v/>
       </c>
       <c r="G101">
-        <f>$B101+0.0048</f>
+        <f>$B101+0.0053</f>
         <v/>
       </c>
       <c r="H101">
-        <f>$B101+-0.0048</f>
+        <f>$B101+-0.0053</f>
         <v/>
       </c>
     </row>
@@ -6513,19 +6520,19 @@
         <v/>
       </c>
       <c r="E102">
-        <f>$B102+1.7938</f>
+        <f>$B102+1.5689</f>
         <v/>
       </c>
       <c r="F102">
-        <f>$B102+-1.1942</f>
+        <f>$B102+-1.0441</f>
         <v/>
       </c>
       <c r="G102">
-        <f>$B102+0.0045</f>
+        <f>$B102+0.005</f>
         <v/>
       </c>
       <c r="H102">
-        <f>$B102+-0.0045</f>
+        <f>$B102+-0.005</f>
         <v/>
       </c>
     </row>
@@ -6546,19 +6553,19 @@
         <v/>
       </c>
       <c r="E103">
-        <f>$B103+1.7942</f>
+        <f>$B103+1.5693</f>
         <v/>
       </c>
       <c r="F103">
-        <f>$B103+-1.1945</f>
+        <f>$B103+-1.0445</f>
         <v/>
       </c>
       <c r="G103">
-        <f>$B103+0.0043</f>
+        <f>$B103+0.0047</f>
         <v/>
       </c>
       <c r="H103">
-        <f>$B103+-0.0043</f>
+        <f>$B103+-0.0047</f>
         <v/>
       </c>
     </row>
@@ -6579,19 +6586,19 @@
         <v/>
       </c>
       <c r="E104">
-        <f>$B104+1.7945</f>
+        <f>$B104+1.5696</f>
         <v/>
       </c>
       <c r="F104">
-        <f>$B104+-1.1949</f>
+        <f>$B104+-1.0448</f>
         <v/>
       </c>
       <c r="G104">
-        <f>$B104+0.004</f>
+        <f>$B104+0.0044</f>
         <v/>
       </c>
       <c r="H104">
-        <f>$B104+-0.004</f>
+        <f>$B104+-0.0044</f>
         <v/>
       </c>
     </row>
@@ -6612,19 +6619,19 @@
         <v/>
       </c>
       <c r="E105">
-        <f>$B105+1.7949</f>
+        <f>$B105+1.5699</f>
         <v/>
       </c>
       <c r="F105">
-        <f>$B105+-1.1952</f>
+        <f>$B105+-1.0451</f>
         <v/>
       </c>
       <c r="G105">
-        <f>$B105+0.0038</f>
+        <f>$B105+0.0041</f>
         <v/>
       </c>
       <c r="H105">
-        <f>$B105+-0.0038</f>
+        <f>$B105+-0.0041</f>
         <v/>
       </c>
     </row>
@@ -6645,19 +6652,19 @@
         <v/>
       </c>
       <c r="E106">
-        <f>$B106+1.7952</f>
+        <f>$B106+1.5703</f>
         <v/>
       </c>
       <c r="F106">
-        <f>$B106+-1.1955</f>
+        <f>$B106+-1.0454</f>
         <v/>
       </c>
       <c r="G106">
-        <f>$B106+0.0035</f>
+        <f>$B106+0.0039</f>
         <v/>
       </c>
       <c r="H106">
-        <f>$B106+-0.0035</f>
+        <f>$B106+-0.0039</f>
         <v/>
       </c>
     </row>
@@ -6678,19 +6685,19 @@
         <v/>
       </c>
       <c r="E107">
-        <f>$B107+1.7955</f>
+        <f>$B107+1.5705</f>
         <v/>
       </c>
       <c r="F107">
-        <f>$B107+-1.1958</f>
+        <f>$B107+-1.0457</f>
         <v/>
       </c>
       <c r="G107">
-        <f>$B107+0.0033</f>
+        <f>$B107+0.0036</f>
         <v/>
       </c>
       <c r="H107">
-        <f>$B107+-0.0033</f>
+        <f>$B107+-0.0036</f>
         <v/>
       </c>
     </row>
@@ -6711,19 +6718,19 @@
         <v/>
       </c>
       <c r="E108">
-        <f>$B108+1.7957</f>
+        <f>$B108+1.5708</f>
         <v/>
       </c>
       <c r="F108">
-        <f>$B108+-1.196</f>
+        <f>$B108+-1.0459</f>
         <v/>
       </c>
       <c r="G108">
-        <f>$B108+0.0031</f>
+        <f>$B108+0.0034</f>
         <v/>
       </c>
       <c r="H108">
-        <f>$B108+-0.0031</f>
+        <f>$B108+-0.0034</f>
         <v/>
       </c>
     </row>
@@ -6744,19 +6751,19 @@
         <v/>
       </c>
       <c r="E109">
-        <f>$B109+1.796</f>
+        <f>$B109+1.5711</f>
         <v/>
       </c>
       <c r="F109">
-        <f>$B109+-1.1963</f>
+        <f>$B109+-1.0462</f>
         <v/>
       </c>
       <c r="G109">
-        <f>$B109+0.0029</f>
+        <f>$B109+0.0032</f>
         <v/>
       </c>
       <c r="H109">
-        <f>$B109+-0.0029</f>
+        <f>$B109+-0.0032</f>
         <v/>
       </c>
     </row>
@@ -6777,19 +6784,19 @@
         <v/>
       </c>
       <c r="E110">
-        <f>$B110+1.7962</f>
+        <f>$B110+1.5713</f>
         <v/>
       </c>
       <c r="F110">
-        <f>$B110+-1.1965</f>
+        <f>$B110+-1.0464</f>
         <v/>
       </c>
       <c r="G110">
-        <f>$B110+0.0027</f>
+        <f>$B110+0.003</f>
         <v/>
       </c>
       <c r="H110">
-        <f>$B110+-0.0027</f>
+        <f>$B110+-0.003</f>
         <v/>
       </c>
     </row>
@@ -6810,19 +6817,19 @@
         <v/>
       </c>
       <c r="E111">
-        <f>$B111+1.7965</f>
+        <f>$B111+1.5715</f>
         <v/>
       </c>
       <c r="F111">
-        <f>$B111+-1.1967</f>
+        <f>$B111+-1.0466</f>
         <v/>
       </c>
       <c r="G111">
-        <f>$B111+0.0026</f>
+        <f>$B111+0.0028</f>
         <v/>
       </c>
       <c r="H111">
-        <f>$B111+-0.0026</f>
+        <f>$B111+-0.0028</f>
         <v/>
       </c>
     </row>
@@ -6843,19 +6850,19 @@
         <v/>
       </c>
       <c r="E112">
-        <f>$B112+1.7967</f>
+        <f>$B112+1.5717</f>
         <v/>
       </c>
       <c r="F112">
-        <f>$B112+-1.1969</f>
+        <f>$B112+-1.0468</f>
         <v/>
       </c>
       <c r="G112">
-        <f>$B112+0.0024</f>
+        <f>$B112+0.0027</f>
         <v/>
       </c>
       <c r="H112">
-        <f>$B112+-0.0024</f>
+        <f>$B112+-0.0027</f>
         <v/>
       </c>
     </row>
@@ -6876,19 +6883,19 @@
         <v/>
       </c>
       <c r="E113">
-        <f>$B113+1.7969</f>
+        <f>$B113+1.5719</f>
         <v/>
       </c>
       <c r="F113">
-        <f>$B113+-1.1971</f>
+        <f>$B113+-1.047</f>
         <v/>
       </c>
       <c r="G113">
-        <f>$B113+0.0023</f>
+        <f>$B113+0.0025</f>
         <v/>
       </c>
       <c r="H113">
-        <f>$B113+-0.0023</f>
+        <f>$B113+-0.0025</f>
         <v/>
       </c>
     </row>
@@ -6909,19 +6916,19 @@
         <v/>
       </c>
       <c r="E114">
-        <f>$B114+1.7971</f>
+        <f>$B114+1.5721</f>
         <v/>
       </c>
       <c r="F114">
-        <f>$B114+-1.1973</f>
+        <f>$B114+-1.0472</f>
         <v/>
       </c>
       <c r="G114">
-        <f>$B114+0.0021</f>
+        <f>$B114+0.0024</f>
         <v/>
       </c>
       <c r="H114">
-        <f>$B114+-0.0021</f>
+        <f>$B114+-0.0024</f>
         <v/>
       </c>
     </row>
@@ -6942,19 +6949,19 @@
         <v/>
       </c>
       <c r="E115">
-        <f>$B115+1.7972</f>
+        <f>$B115+1.5723</f>
         <v/>
       </c>
       <c r="F115">
-        <f>$B115+-1.1974</f>
+        <f>$B115+-1.0474</f>
         <v/>
       </c>
       <c r="G115">
-        <f>$B115+0.002</f>
+        <f>$B115+0.0022</f>
         <v/>
       </c>
       <c r="H115">
-        <f>$B115+-0.002</f>
+        <f>$B115+-0.0022</f>
         <v/>
       </c>
     </row>
@@ -6975,19 +6982,19 @@
         <v/>
       </c>
       <c r="E116">
-        <f>$B116+1.7974</f>
+        <f>$B116+1.5725</f>
         <v/>
       </c>
       <c r="F116">
-        <f>$B116+-1.1976</f>
+        <f>$B116+-1.0475</f>
         <v/>
       </c>
       <c r="G116">
-        <f>$B116+0.0019</f>
+        <f>$B116+0.0021</f>
         <v/>
       </c>
       <c r="H116">
-        <f>$B116+-0.0019</f>
+        <f>$B116+-0.0021</f>
         <v/>
       </c>
     </row>
@@ -7008,19 +7015,19 @@
         <v/>
       </c>
       <c r="E117">
-        <f>$B117+1.7976</f>
+        <f>$B117+1.5726</f>
         <v/>
       </c>
       <c r="F117">
-        <f>$B117+-1.1977</f>
+        <f>$B117+-1.0477</f>
         <v/>
       </c>
       <c r="G117">
-        <f>$B117+0.0018</f>
+        <f>$B117+0.002</f>
         <v/>
       </c>
       <c r="H117">
-        <f>$B117+-0.0018</f>
+        <f>$B117+-0.002</f>
         <v/>
       </c>
     </row>
@@ -7041,19 +7048,19 @@
         <v/>
       </c>
       <c r="E118">
-        <f>$B118+1.7977</f>
+        <f>$B118+1.5728</f>
         <v/>
       </c>
       <c r="F118">
-        <f>$B118+-1.1979</f>
+        <f>$B118+-1.0478</f>
         <v/>
       </c>
       <c r="G118">
-        <f>$B118+0.0017</f>
+        <f>$B118+0.0018</f>
         <v/>
       </c>
       <c r="H118">
-        <f>$B118+-0.0017</f>
+        <f>$B118+-0.0018</f>
         <v/>
       </c>
     </row>
@@ -7074,19 +7081,19 @@
         <v/>
       </c>
       <c r="E119">
-        <f>$B119+1.7979</f>
+        <f>$B119+1.5729</f>
         <v/>
       </c>
       <c r="F119">
-        <f>$B119+-1.198</f>
+        <f>$B119+-1.048</f>
         <v/>
       </c>
       <c r="G119">
-        <f>$B119+0.0016</f>
+        <f>$B119+0.0017</f>
         <v/>
       </c>
       <c r="H119">
-        <f>$B119+-0.0016</f>
+        <f>$B119+-0.0017</f>
         <v/>
       </c>
     </row>
@@ -7107,19 +7114,19 @@
         <v/>
       </c>
       <c r="E120">
-        <f>$B120+1.798</f>
+        <f>$B120+1.573</f>
         <v/>
       </c>
       <c r="F120">
-        <f>$B120+-1.1981</f>
+        <f>$B120+-1.0481</f>
         <v/>
       </c>
       <c r="G120">
-        <f>$B120+0.0015</f>
+        <f>$B120+0.0016</f>
         <v/>
       </c>
       <c r="H120">
-        <f>$B120+-0.0015</f>
+        <f>$B120+-0.0016</f>
         <v/>
       </c>
     </row>
@@ -7140,19 +7147,19 @@
         <v/>
       </c>
       <c r="E121">
-        <f>$B121+1.7981</f>
+        <f>$B121+1.5731</f>
         <v/>
       </c>
       <c r="F121">
-        <f>$B121+-1.1982</f>
+        <f>$B121+-1.0482</f>
         <v/>
       </c>
       <c r="G121">
-        <f>$B121+0.0014</f>
+        <f>$B121+0.0015</f>
         <v/>
       </c>
       <c r="H121">
-        <f>$B121+-0.0014</f>
+        <f>$B121+-0.0015</f>
         <v/>
       </c>
     </row>
@@ -7208,27 +7215,27 @@
         <v/>
       </c>
       <c r="C124">
-        <f>VLOOKUP($A124,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A124,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D124">
-        <f>VLOOKUP($A124,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A124,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E124">
-        <f>VLOOKUP($A124,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A124,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F124">
-        <f>VLOOKUP($A124,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A124,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G124">
-        <f>VLOOKUP($A124,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A124,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H124">
-        <f>VLOOKUP($A124,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A124,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7242,27 +7249,27 @@
         <v/>
       </c>
       <c r="C125">
-        <f>VLOOKUP($A125,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A125,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D125">
-        <f>VLOOKUP($A125,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A125,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E125">
-        <f>VLOOKUP($A125,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A125,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F125">
-        <f>VLOOKUP($A125,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A125,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G125">
-        <f>VLOOKUP($A125,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A125,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H125">
-        <f>VLOOKUP($A125,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A125,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7276,27 +7283,27 @@
         <v/>
       </c>
       <c r="C126">
-        <f>VLOOKUP($A126,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A126,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D126">
-        <f>VLOOKUP($A126,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A126,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E126">
-        <f>VLOOKUP($A126,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A126,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F126">
-        <f>VLOOKUP($A126,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A126,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G126">
-        <f>VLOOKUP($A126,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A126,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H126">
-        <f>VLOOKUP($A126,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A126,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7310,27 +7317,27 @@
         <v/>
       </c>
       <c r="C127">
-        <f>VLOOKUP($A127,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A127,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D127">
-        <f>VLOOKUP($A127,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A127,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E127">
-        <f>VLOOKUP($A127,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A127,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F127">
-        <f>VLOOKUP($A127,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A127,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G127">
-        <f>VLOOKUP($A127,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A127,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H127">
-        <f>VLOOKUP($A127,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A127,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7344,27 +7351,27 @@
         <v/>
       </c>
       <c r="C128">
-        <f>VLOOKUP($A128,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A128,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D128">
-        <f>VLOOKUP($A128,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A128,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E128">
-        <f>VLOOKUP($A128,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A128,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F128">
-        <f>VLOOKUP($A128,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A128,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G128">
-        <f>VLOOKUP($A128,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A128,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H128">
-        <f>VLOOKUP($A128,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A128,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7378,27 +7385,27 @@
         <v/>
       </c>
       <c r="C129">
-        <f>VLOOKUP($A129,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A129,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D129">
-        <f>VLOOKUP($A129,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A129,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E129">
-        <f>VLOOKUP($A129,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A129,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F129">
-        <f>VLOOKUP($A129,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A129,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G129">
-        <f>VLOOKUP($A129,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A129,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H129">
-        <f>VLOOKUP($A129,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A129,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7412,27 +7419,27 @@
         <v/>
       </c>
       <c r="C130">
-        <f>VLOOKUP($A130,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A130,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D130">
-        <f>VLOOKUP($A130,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A130,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E130">
-        <f>VLOOKUP($A130,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A130,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F130">
-        <f>VLOOKUP($A130,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A130,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G130">
-        <f>VLOOKUP($A130,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A130,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H130">
-        <f>VLOOKUP($A130,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A130,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7446,27 +7453,27 @@
         <v/>
       </c>
       <c r="C131">
-        <f>VLOOKUP($A131,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A131,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D131">
-        <f>VLOOKUP($A131,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A131,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E131">
-        <f>VLOOKUP($A131,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A131,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F131">
-        <f>VLOOKUP($A131,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A131,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G131">
-        <f>VLOOKUP($A131,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A131,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H131">
-        <f>VLOOKUP($A131,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A131,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7480,27 +7487,27 @@
         <v/>
       </c>
       <c r="C132">
-        <f>VLOOKUP($A132,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A132,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D132">
-        <f>VLOOKUP($A132,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A132,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E132">
-        <f>VLOOKUP($A132,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A132,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F132">
-        <f>VLOOKUP($A132,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A132,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G132">
-        <f>VLOOKUP($A132,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A132,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H132">
-        <f>VLOOKUP($A132,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A132,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7514,27 +7521,27 @@
         <v/>
       </c>
       <c r="C133">
-        <f>VLOOKUP($A133,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A133,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D133">
-        <f>VLOOKUP($A133,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A133,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E133">
-        <f>VLOOKUP($A133,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A133,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F133">
-        <f>VLOOKUP($A133,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A133,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G133">
-        <f>VLOOKUP($A133,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A133,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H133">
-        <f>VLOOKUP($A133,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A133,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7548,27 +7555,27 @@
         <v/>
       </c>
       <c r="C134">
-        <f>VLOOKUP($A134,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A134,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D134">
-        <f>VLOOKUP($A134,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A134,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E134">
-        <f>VLOOKUP($A134,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A134,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F134">
-        <f>VLOOKUP($A134,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A134,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G134">
-        <f>VLOOKUP($A134,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A134,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H134">
-        <f>VLOOKUP($A134,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A134,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7582,27 +7589,27 @@
         <v/>
       </c>
       <c r="C135">
-        <f>VLOOKUP($A135,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A135,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D135">
-        <f>VLOOKUP($A135,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A135,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E135">
-        <f>VLOOKUP($A135,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A135,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F135">
-        <f>VLOOKUP($A135,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A135,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G135">
-        <f>VLOOKUP($A135,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A135,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H135">
-        <f>VLOOKUP($A135,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A135,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7616,27 +7623,27 @@
         <v/>
       </c>
       <c r="C136">
-        <f>VLOOKUP($A136,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A136,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D136">
-        <f>VLOOKUP($A136,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A136,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E136">
-        <f>VLOOKUP($A136,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A136,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F136">
-        <f>VLOOKUP($A136,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A136,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G136">
-        <f>VLOOKUP($A136,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A136,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H136">
-        <f>VLOOKUP($A136,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A136,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7650,27 +7657,27 @@
         <v/>
       </c>
       <c r="C137">
-        <f>VLOOKUP($A137,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A137,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D137">
-        <f>VLOOKUP($A137,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A137,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E137">
-        <f>VLOOKUP($A137,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A137,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F137">
-        <f>VLOOKUP($A137,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A137,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G137">
-        <f>VLOOKUP($A137,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A137,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H137">
-        <f>VLOOKUP($A137,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A137,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7684,27 +7691,27 @@
         <v/>
       </c>
       <c r="C138">
-        <f>VLOOKUP($A138,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A138,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D138">
-        <f>VLOOKUP($A138,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A138,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E138">
-        <f>VLOOKUP($A138,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A138,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F138">
-        <f>VLOOKUP($A138,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A138,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G138">
-        <f>VLOOKUP($A138,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A138,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H138">
-        <f>VLOOKUP($A138,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A138,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7718,27 +7725,27 @@
         <v/>
       </c>
       <c r="C139">
-        <f>VLOOKUP($A139,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A139,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D139">
-        <f>VLOOKUP($A139,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A139,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E139">
-        <f>VLOOKUP($A139,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A139,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F139">
-        <f>VLOOKUP($A139,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A139,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G139">
-        <f>VLOOKUP($A139,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A139,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H139">
-        <f>VLOOKUP($A139,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A139,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7752,27 +7759,27 @@
         <v/>
       </c>
       <c r="C140">
-        <f>VLOOKUP($A140,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A140,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D140">
-        <f>VLOOKUP($A140,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A140,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E140">
-        <f>VLOOKUP($A140,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A140,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F140">
-        <f>VLOOKUP($A140,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A140,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G140">
-        <f>VLOOKUP($A140,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A140,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H140">
-        <f>VLOOKUP($A140,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A140,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7786,27 +7793,27 @@
         <v/>
       </c>
       <c r="C141">
-        <f>VLOOKUP($A141,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A141,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D141">
-        <f>VLOOKUP($A141,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A141,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E141">
-        <f>VLOOKUP($A141,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A141,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F141">
-        <f>VLOOKUP($A141,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A141,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G141">
-        <f>VLOOKUP($A141,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A141,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H141">
-        <f>VLOOKUP($A141,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A141,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7820,27 +7827,27 @@
         <v/>
       </c>
       <c r="C142">
-        <f>VLOOKUP($A142,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A142,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D142">
-        <f>VLOOKUP($A142,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A142,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E142">
-        <f>VLOOKUP($A142,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A142,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F142">
-        <f>VLOOKUP($A142,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A142,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G142">
-        <f>VLOOKUP($A142,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A142,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H142">
-        <f>VLOOKUP($A142,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A142,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7854,27 +7861,27 @@
         <v/>
       </c>
       <c r="C143">
-        <f>VLOOKUP($A143,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A143,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D143">
-        <f>VLOOKUP($A143,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A143,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E143">
-        <f>VLOOKUP($A143,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A143,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F143">
-        <f>VLOOKUP($A143,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A143,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G143">
-        <f>VLOOKUP($A143,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A143,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H143">
-        <f>VLOOKUP($A143,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A143,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7888,27 +7895,27 @@
         <v/>
       </c>
       <c r="C144">
-        <f>VLOOKUP($A144,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A144,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D144">
-        <f>VLOOKUP($A144,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A144,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E144">
-        <f>VLOOKUP($A144,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A144,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F144">
-        <f>VLOOKUP($A144,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A144,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G144">
-        <f>VLOOKUP($A144,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A144,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H144">
-        <f>VLOOKUP($A144,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A144,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7922,27 +7929,27 @@
         <v/>
       </c>
       <c r="C145">
-        <f>VLOOKUP($A145,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A145,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D145">
-        <f>VLOOKUP($A145,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A145,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E145">
-        <f>VLOOKUP($A145,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A145,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F145">
-        <f>VLOOKUP($A145,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A145,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G145">
-        <f>VLOOKUP($A145,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A145,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H145">
-        <f>VLOOKUP($A145,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A145,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7956,27 +7963,27 @@
         <v/>
       </c>
       <c r="C146">
-        <f>VLOOKUP($A146,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A146,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D146">
-        <f>VLOOKUP($A146,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A146,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E146">
-        <f>VLOOKUP($A146,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A146,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F146">
-        <f>VLOOKUP($A146,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A146,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G146">
-        <f>VLOOKUP($A146,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A146,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H146">
-        <f>VLOOKUP($A146,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A146,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -7990,27 +7997,27 @@
         <v/>
       </c>
       <c r="C147">
-        <f>VLOOKUP($A147,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A147,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D147">
-        <f>VLOOKUP($A147,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A147,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E147">
-        <f>VLOOKUP($A147,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A147,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F147">
-        <f>VLOOKUP($A147,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A147,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G147">
-        <f>VLOOKUP($A147,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A147,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H147">
-        <f>VLOOKUP($A147,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A147,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8024,27 +8031,27 @@
         <v/>
       </c>
       <c r="C148">
-        <f>VLOOKUP($A148,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A148,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D148">
-        <f>VLOOKUP($A148,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A148,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E148">
-        <f>VLOOKUP($A148,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A148,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F148">
-        <f>VLOOKUP($A148,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A148,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G148">
-        <f>VLOOKUP($A148,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A148,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H148">
-        <f>VLOOKUP($A148,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A148,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8058,27 +8065,27 @@
         <v/>
       </c>
       <c r="C149">
-        <f>VLOOKUP($A149,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A149,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D149">
-        <f>VLOOKUP($A149,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A149,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E149">
-        <f>VLOOKUP($A149,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A149,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F149">
-        <f>VLOOKUP($A149,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A149,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G149">
-        <f>VLOOKUP($A149,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A149,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H149">
-        <f>VLOOKUP($A149,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A149,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8092,27 +8099,27 @@
         <v/>
       </c>
       <c r="C150">
-        <f>VLOOKUP($A150,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A150,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D150">
-        <f>VLOOKUP($A150,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A150,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E150">
-        <f>VLOOKUP($A150,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A150,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F150">
-        <f>VLOOKUP($A150,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A150,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G150">
-        <f>VLOOKUP($A150,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A150,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H150">
-        <f>VLOOKUP($A150,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A150,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8126,27 +8133,27 @@
         <v/>
       </c>
       <c r="C151">
-        <f>VLOOKUP($A151,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A151,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D151">
-        <f>VLOOKUP($A151,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A151,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E151">
-        <f>VLOOKUP($A151,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A151,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F151">
-        <f>VLOOKUP($A151,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A151,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G151">
-        <f>VLOOKUP($A151,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A151,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H151">
-        <f>VLOOKUP($A151,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A151,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8160,27 +8167,27 @@
         <v/>
       </c>
       <c r="C152">
-        <f>VLOOKUP($A152,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A152,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D152">
-        <f>VLOOKUP($A152,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A152,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E152">
-        <f>VLOOKUP($A152,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A152,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F152">
-        <f>VLOOKUP($A152,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A152,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G152">
-        <f>VLOOKUP($A152,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A152,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H152">
-        <f>VLOOKUP($A152,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A152,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8194,27 +8201,27 @@
         <v/>
       </c>
       <c r="C153">
-        <f>VLOOKUP($A153,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A153,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D153">
-        <f>VLOOKUP($A153,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A153,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E153">
-        <f>VLOOKUP($A153,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A153,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F153">
-        <f>VLOOKUP($A153,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A153,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G153">
-        <f>VLOOKUP($A153,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A153,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H153">
-        <f>VLOOKUP($A153,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A153,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8228,27 +8235,27 @@
         <v/>
       </c>
       <c r="C154">
-        <f>VLOOKUP($A154,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A154,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D154">
-        <f>VLOOKUP($A154,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A154,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E154">
-        <f>VLOOKUP($A154,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A154,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F154">
-        <f>VLOOKUP($A154,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A154,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G154">
-        <f>VLOOKUP($A154,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A154,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H154">
-        <f>VLOOKUP($A154,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A154,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8262,27 +8269,27 @@
         <v/>
       </c>
       <c r="C155">
-        <f>VLOOKUP($A155,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A155,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D155">
-        <f>VLOOKUP($A155,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A155,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E155">
-        <f>VLOOKUP($A155,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A155,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F155">
-        <f>VLOOKUP($A155,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A155,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G155">
-        <f>VLOOKUP($A155,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A155,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H155">
-        <f>VLOOKUP($A155,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A155,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8296,27 +8303,27 @@
         <v/>
       </c>
       <c r="C156">
-        <f>VLOOKUP($A156,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A156,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D156">
-        <f>VLOOKUP($A156,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A156,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E156">
-        <f>VLOOKUP($A156,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A156,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F156">
-        <f>VLOOKUP($A156,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A156,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G156">
-        <f>VLOOKUP($A156,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A156,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H156">
-        <f>VLOOKUP($A156,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A156,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8330,27 +8337,27 @@
         <v/>
       </c>
       <c r="C157">
-        <f>VLOOKUP($A157,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A157,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D157">
-        <f>VLOOKUP($A157,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A157,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E157">
-        <f>VLOOKUP($A157,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A157,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F157">
-        <f>VLOOKUP($A157,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A157,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G157">
-        <f>VLOOKUP($A157,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A157,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H157">
-        <f>VLOOKUP($A157,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A157,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8364,27 +8371,27 @@
         <v/>
       </c>
       <c r="C158">
-        <f>VLOOKUP($A158,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A158,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D158">
-        <f>VLOOKUP($A158,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A158,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E158">
-        <f>VLOOKUP($A158,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A158,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F158">
-        <f>VLOOKUP($A158,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A158,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G158">
-        <f>VLOOKUP($A158,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A158,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H158">
-        <f>VLOOKUP($A158,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A158,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8398,27 +8405,27 @@
         <v/>
       </c>
       <c r="C159">
-        <f>VLOOKUP($A159,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A159,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D159">
-        <f>VLOOKUP($A159,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A159,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E159">
-        <f>VLOOKUP($A159,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A159,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F159">
-        <f>VLOOKUP($A159,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A159,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G159">
-        <f>VLOOKUP($A159,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A159,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H159">
-        <f>VLOOKUP($A159,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A159,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8432,27 +8439,27 @@
         <v/>
       </c>
       <c r="C160">
-        <f>VLOOKUP($A160,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A160,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D160">
-        <f>VLOOKUP($A160,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A160,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E160">
-        <f>VLOOKUP($A160,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A160,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F160">
-        <f>VLOOKUP($A160,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A160,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G160">
-        <f>VLOOKUP($A160,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A160,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H160">
-        <f>VLOOKUP($A160,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A160,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8466,27 +8473,27 @@
         <v/>
       </c>
       <c r="C161">
-        <f>VLOOKUP($A161,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A161,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D161">
-        <f>VLOOKUP($A161,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A161,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E161">
-        <f>VLOOKUP($A161,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A161,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F161">
-        <f>VLOOKUP($A161,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A161,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G161">
-        <f>VLOOKUP($A161,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A161,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H161">
-        <f>VLOOKUP($A161,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A161,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8500,27 +8507,27 @@
         <v/>
       </c>
       <c r="C162">
-        <f>VLOOKUP($A162,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A162,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D162">
-        <f>VLOOKUP($A162,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A162,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E162">
-        <f>VLOOKUP($A162,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A162,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F162">
-        <f>VLOOKUP($A162,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A162,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G162">
-        <f>VLOOKUP($A162,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A162,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H162">
-        <f>VLOOKUP($A162,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A162,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8534,27 +8541,27 @@
         <v/>
       </c>
       <c r="C163">
-        <f>VLOOKUP($A163,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A163,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D163">
-        <f>VLOOKUP($A163,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A163,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E163">
-        <f>VLOOKUP($A163,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A163,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F163">
-        <f>VLOOKUP($A163,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A163,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G163">
-        <f>VLOOKUP($A163,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A163,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H163">
-        <f>VLOOKUP($A163,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A163,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8568,27 +8575,27 @@
         <v/>
       </c>
       <c r="C164">
-        <f>VLOOKUP($A164,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A164,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D164">
-        <f>VLOOKUP($A164,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A164,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E164">
-        <f>VLOOKUP($A164,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A164,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F164">
-        <f>VLOOKUP($A164,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A164,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G164">
-        <f>VLOOKUP($A164,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A164,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H164">
-        <f>VLOOKUP($A164,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A164,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8602,27 +8609,27 @@
         <v/>
       </c>
       <c r="C165">
-        <f>VLOOKUP($A165,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A165,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D165">
-        <f>VLOOKUP($A165,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A165,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E165">
-        <f>VLOOKUP($A165,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A165,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F165">
-        <f>VLOOKUP($A165,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A165,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G165">
-        <f>VLOOKUP($A165,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A165,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H165">
-        <f>VLOOKUP($A165,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A165,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8636,27 +8643,27 @@
         <v/>
       </c>
       <c r="C166">
-        <f>VLOOKUP($A166,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A166,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D166">
-        <f>VLOOKUP($A166,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A166,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E166">
-        <f>VLOOKUP($A166,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A166,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F166">
-        <f>VLOOKUP($A166,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A166,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G166">
-        <f>VLOOKUP($A166,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A166,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H166">
-        <f>VLOOKUP($A166,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A166,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8670,27 +8677,27 @@
         <v/>
       </c>
       <c r="C167">
-        <f>VLOOKUP($A167,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A167,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D167">
-        <f>VLOOKUP($A167,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A167,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E167">
-        <f>VLOOKUP($A167,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A167,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F167">
-        <f>VLOOKUP($A167,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A167,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G167">
-        <f>VLOOKUP($A167,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A167,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H167">
-        <f>VLOOKUP($A167,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A167,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8704,27 +8711,27 @@
         <v/>
       </c>
       <c r="C168">
-        <f>VLOOKUP($A168,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A168,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D168">
-        <f>VLOOKUP($A168,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A168,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E168">
-        <f>VLOOKUP($A168,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A168,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F168">
-        <f>VLOOKUP($A168,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A168,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G168">
-        <f>VLOOKUP($A168,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A168,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H168">
-        <f>VLOOKUP($A168,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A168,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8738,27 +8745,27 @@
         <v/>
       </c>
       <c r="C169">
-        <f>VLOOKUP($A169,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A169,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D169">
-        <f>VLOOKUP($A169,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A169,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E169">
-        <f>VLOOKUP($A169,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A169,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F169">
-        <f>VLOOKUP($A169,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A169,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G169">
-        <f>VLOOKUP($A169,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A169,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H169">
-        <f>VLOOKUP($A169,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A169,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8772,27 +8779,27 @@
         <v/>
       </c>
       <c r="C170">
-        <f>VLOOKUP($A170,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A170,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D170">
-        <f>VLOOKUP($A170,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A170,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E170">
-        <f>VLOOKUP($A170,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A170,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F170">
-        <f>VLOOKUP($A170,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A170,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G170">
-        <f>VLOOKUP($A170,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A170,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H170">
-        <f>VLOOKUP($A170,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A170,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8806,27 +8813,27 @@
         <v/>
       </c>
       <c r="C171">
-        <f>VLOOKUP($A171,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A171,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D171">
-        <f>VLOOKUP($A171,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A171,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E171">
-        <f>VLOOKUP($A171,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A171,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F171">
-        <f>VLOOKUP($A171,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A171,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G171">
-        <f>VLOOKUP($A171,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A171,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H171">
-        <f>VLOOKUP($A171,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A171,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8840,27 +8847,27 @@
         <v/>
       </c>
       <c r="C172">
-        <f>VLOOKUP($A172,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A172,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D172">
-        <f>VLOOKUP($A172,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A172,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E172">
-        <f>VLOOKUP($A172,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A172,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F172">
-        <f>VLOOKUP($A172,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A172,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G172">
-        <f>VLOOKUP($A172,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A172,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H172">
-        <f>VLOOKUP($A172,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A172,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8874,27 +8881,27 @@
         <v/>
       </c>
       <c r="C173">
-        <f>VLOOKUP($A173,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A173,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D173">
-        <f>VLOOKUP($A173,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A173,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E173">
-        <f>VLOOKUP($A173,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A173,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F173">
-        <f>VLOOKUP($A173,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A173,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G173">
-        <f>VLOOKUP($A173,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A173,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H173">
-        <f>VLOOKUP($A173,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A173,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8908,27 +8915,27 @@
         <v/>
       </c>
       <c r="C174">
-        <f>VLOOKUP($A174,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A174,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D174">
-        <f>VLOOKUP($A174,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A174,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E174">
-        <f>VLOOKUP($A174,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A174,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F174">
-        <f>VLOOKUP($A174,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A174,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G174">
-        <f>VLOOKUP($A174,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A174,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H174">
-        <f>VLOOKUP($A174,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A174,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8942,27 +8949,27 @@
         <v/>
       </c>
       <c r="C175">
-        <f>VLOOKUP($A175,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A175,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D175">
-        <f>VLOOKUP($A175,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A175,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E175">
-        <f>VLOOKUP($A175,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A175,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F175">
-        <f>VLOOKUP($A175,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A175,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G175">
-        <f>VLOOKUP($A175,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A175,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H175">
-        <f>VLOOKUP($A175,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A175,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -8976,27 +8983,27 @@
         <v/>
       </c>
       <c r="C176">
-        <f>VLOOKUP($A176,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A176,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D176">
-        <f>VLOOKUP($A176,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A176,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E176">
-        <f>VLOOKUP($A176,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A176,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F176">
-        <f>VLOOKUP($A176,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A176,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G176">
-        <f>VLOOKUP($A176,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A176,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H176">
-        <f>VLOOKUP($A176,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A176,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -9010,27 +9017,27 @@
         <v/>
       </c>
       <c r="C177">
-        <f>VLOOKUP($A177,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A177,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D177">
-        <f>VLOOKUP($A177,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A177,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E177">
-        <f>VLOOKUP($A177,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A177,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F177">
-        <f>VLOOKUP($A177,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A177,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G177">
-        <f>VLOOKUP($A177,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A177,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H177">
-        <f>VLOOKUP($A177,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A177,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -9044,27 +9051,27 @@
         <v/>
       </c>
       <c r="C178">
-        <f>VLOOKUP($A178,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A178,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D178">
-        <f>VLOOKUP($A178,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A178,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E178">
-        <f>VLOOKUP($A178,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A178,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F178">
-        <f>VLOOKUP($A178,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A178,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G178">
-        <f>VLOOKUP($A178,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A178,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H178">
-        <f>VLOOKUP($A178,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A178,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -9078,27 +9085,27 @@
         <v/>
       </c>
       <c r="C179">
-        <f>VLOOKUP($A179,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A179,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D179">
-        <f>VLOOKUP($A179,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A179,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E179">
-        <f>VLOOKUP($A179,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A179,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F179">
-        <f>VLOOKUP($A179,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A179,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G179">
-        <f>VLOOKUP($A179,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A179,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H179">
-        <f>VLOOKUP($A179,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A179,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -9112,27 +9119,27 @@
         <v/>
       </c>
       <c r="C180">
-        <f>VLOOKUP($A180,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A180,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D180">
-        <f>VLOOKUP($A180,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A180,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E180">
-        <f>VLOOKUP($A180,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A180,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F180">
-        <f>VLOOKUP($A180,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A180,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G180">
-        <f>VLOOKUP($A180,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A180,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H180">
-        <f>VLOOKUP($A180,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A180,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -9146,27 +9153,27 @@
         <v/>
       </c>
       <c r="C181">
-        <f>VLOOKUP($A181,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A181,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D181">
-        <f>VLOOKUP($A181,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A181,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E181">
-        <f>VLOOKUP($A181,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A181,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F181">
-        <f>VLOOKUP($A181,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A181,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G181">
-        <f>VLOOKUP($A181,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A181,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H181">
-        <f>VLOOKUP($A181,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A181,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -9180,27 +9187,27 @@
         <v/>
       </c>
       <c r="C182">
-        <f>VLOOKUP($A182,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A182,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D182">
-        <f>VLOOKUP($A182,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A182,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E182">
-        <f>VLOOKUP($A182,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A182,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F182">
-        <f>VLOOKUP($A182,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A182,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G182">
-        <f>VLOOKUP($A182,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A182,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H182">
-        <f>VLOOKUP($A182,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A182,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
@@ -9214,27 +9221,27 @@
         <v/>
       </c>
       <c r="C183">
-        <f>VLOOKUP($A183,$A$2:$H$121,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A183,$A$2:$H$121,3,FALSE),0)</f>
         <v/>
       </c>
       <c r="D183">
-        <f>VLOOKUP($A183,$A$2:$H$121,4,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A183,$A$2:$H$121,4,FALSE),0)</f>
         <v/>
       </c>
       <c r="E183">
-        <f>VLOOKUP($A183,$A$2:$H$121,5,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A183,$A$2:$H$121,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="F183">
-        <f>VLOOKUP($A183,$A$2:$H$121,6,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A183,$A$2:$H$121,6,FALSE),0)</f>
         <v/>
       </c>
       <c r="G183">
-        <f>VLOOKUP($A183,$A$2:$H$121,7,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A183,$A$2:$H$121,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="H183">
-        <f>VLOOKUP($A183,$A$2:$H$121,8,FALSE)</f>
+        <f>IFERROR(VLOOKUP($A183,$A$2:$H$121,8,FALSE),0)</f>
         <v/>
       </c>
     </row>
